--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5. sep.TidTipEkspertOdds14:00Sundby-ASA AarhusCampoBet 3. DivisionBettingGuru1.88BettingGuru</t>
+          <t>7. sep.TidTipEkspertOdds00:30Corinthians – ChapecoenseBrasilien, Serie ABettingGuru2.00BettingGuru</t>
         </is>
       </c>
     </row>
@@ -467,48 +467,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bettingguru</t>
+          <t>frank-pilantra</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7. sep.TidTipEkspertOdds00:30Corinthians – ChapecoenseBrasilien, Serie ABettingGuru2.00BettingGuru</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>loso</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>5. sep.TidTipEkspertOdds16:00Over 13 hjørne (3-vejs)FC TrollhättanvsEskilsminneLoso6.00Loso</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>loso</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>5. sep.TidTipEkspertOdds16:00Over 4,5 målKarlstadvsAFC EskilstunaLoso4.33Loso</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>5. sep.TidTipEkspertOdds23:30São Paulo – Atletico MGBrasilien – Serie AFrank Pilantra1.50Frank Pilantra</t>
+          <t>6. sep.TidTipEkspertOdds21:00Cruzeiro – Athletico PRBrasileirãoFrank Pilantra1.95Frank Pilantra</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,36 +443,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>bettingguru</t>
+          <t>frank-pilantra</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7. sep.TidTipEkspertOdds00:30Corinthians – ChapecoenseBrasilien, Serie ABettingGuru2.00BettingGuru</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>bettingguru</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>6. sep.TidTipEkspertOdds18:00Brøndby – RandersSuperligaBettingGuru2.02BettingGuru</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>6. sep.TidTipEkspertOdds21:00Cruzeiro – Athletico PRBrasileirãoFrank Pilantra1.95Frank Pilantra</t>
+          <t>9. sep.TidTipEkspertOdds00:00Independiente Santa FevsVasco da GamaCopa SudamericanaFrank Pilantra1.59Frank Pilantra</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6 +449,30 @@
       <c r="B2" t="inlineStr">
         <is>
           <t>9. sep.TidTipEkspertOdds00:00Independiente Santa FevsVasco da GamaCopa SudamericanaFrank Pilantra1.59Frank Pilantra</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>12. sep.TidTipEkspertOdds23:30São PaulovsCorinthiansBrasileirãoFrank Pilantra1.45Frank Pilantra</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>10. sep.TidTipEkspertOdds02:30EstudiantesvsCorinthiansCopa LibertadoresFrank Pilantra1.68Frank Pilantra</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9. sep.TidTipEkspertOdds00:00Independiente Santa FevsVasco da GamaCopa SudamericanaFrank Pilantra1.59Frank Pilantra</t>
+          <t>11. sep.TidTipEkspertOdds02:30Independiente del VallevsFlamengoCopa LibertadoresFrank Pilantra1.90Frank Pilantra</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12. sep.TidTipEkspertOdds23:30São PaulovsCorinthiansBrasileirãoFrank Pilantra1.45Frank Pilantra</t>
+          <t>10. sep.TidTipEkspertOdds02:30EstudiantesvsCorinthiansCopa LibertadoresFrank Pilantra1.68Frank Pilantra</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10. sep.TidTipEkspertOdds02:30EstudiantesvsCorinthiansCopa LibertadoresFrank Pilantra1.68Frank Pilantra</t>
+          <t>9. sep.TidTipEkspertOdds00:00Independiente Santa FevsVasco da GamaCopa SudamericanaFrank Pilantra1.59Frank Pilantra</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>12. sep.TidTipEkspertOdds23:30São PaulovsCorinthiansBrasileirãoFrank Pilantra1.45Frank Pilantra</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>11. sep.TidTipEkspertOdds02:30Independiente del VallevsFlamengoCopa LibertadoresFrank Pilantra1.55Frank Pilantra</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,24 +443,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>frank-pilantra</t>
+          <t>loso</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11. sep.TidTipEkspertOdds02:30Independiente del VallevsFlamengoCopa LibertadoresFrank Pilantra1.90Frank Pilantra</t>
+          <t>9. sep.TidTipEkspertOdds19:00Over 4,5 målSandvikens IFvsIK OddevoldLoso5.60Loso</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>frank-pilantra</t>
+          <t>loso</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10. sep.TidTipEkspertOdds02:30EstudiantesvsCorinthiansCopa LibertadoresFrank Pilantra1.68Frank Pilantra</t>
+          <t>9. sep.TidTipEkspertOdds19:00Over 2,5 målSandvikens IFvsIK OddevoldLoso1.76Loso</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>9. sep.TidTipEkspertOdds00:00Independiente Santa FevsVasco da GamaCopa SudamericanaFrank Pilantra1.59Frank Pilantra</t>
+          <t>11. sep.TidTipEkspertOdds02:30Independiente del VallevsFlamengoCopa LibertadoresFrank Pilantra1.90Frank Pilantra</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12. sep.TidTipEkspertOdds23:30São PaulovsCorinthiansBrasileirãoFrank Pilantra1.45Frank Pilantra</t>
+          <t>10. sep.TidTipEkspertOdds02:30EstudiantesvsCorinthiansCopa LibertadoresFrank Pilantra1.68Frank Pilantra</t>
         </is>
       </c>
     </row>
@@ -495,6 +495,18 @@
         </is>
       </c>
       <c r="B6" t="inlineStr">
+        <is>
+          <t>12. sep.TidTipEkspertOdds23:30São PaulovsCorinthiansBrasileirãoFrank Pilantra1.45Frank Pilantra</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>11. sep.TidTipEkspertOdds02:30Independiente del VallevsFlamengoCopa LibertadoresFrank Pilantra1.55Frank Pilantra</t>
         </is>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,24 +443,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>loso</t>
+          <t>bettingguru</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9. sep.TidTipEkspertOdds19:00Over 4,5 målSandvikens IFvsIK OddevoldLoso5.60Loso</t>
+          <t>13. sep.TidTipEkspertOdds13:00Helsingør Vs SundbyCampoBet 3. DivisionBettingGuru1.58BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>loso</t>
+          <t>bettingguru</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>9. sep.TidTipEkspertOdds19:00Over 2,5 målSandvikens IFvsIK OddevoldLoso1.76Loso</t>
+          <t>13. sep.TidTipEkspertOdds13:00Næstved Vs ThistedCampoBet 2. DivisionBettingGuru1.98BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11. sep.TidTipEkspertOdds02:30Independiente del VallevsFlamengoCopa LibertadoresFrank Pilantra1.90Frank Pilantra</t>
+          <t>11. sep.TidTipEkspertOdds02:30Independiente del VallevsFlamengoCopa LibertadoresFrank Pilantra1.55Frank Pilantra</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10. sep.TidTipEkspertOdds02:30EstudiantesvsCorinthiansCopa LibertadoresFrank Pilantra1.68Frank Pilantra</t>
+          <t>12. sep.TidTipEkspertOdds23:30São PaulovsCorinthiansBrasileirãoFrank Pilantra1.45Frank Pilantra</t>
         </is>
       </c>
     </row>
@@ -496,19 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12. sep.TidTipEkspertOdds23:30São PaulovsCorinthiansBrasileirãoFrank Pilantra1.45Frank Pilantra</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>11. sep.TidTipEkspertOdds02:30Independiente del VallevsFlamengoCopa LibertadoresFrank Pilantra1.55Frank Pilantra</t>
+          <t>11. sep.TidTipEkspertOdds02:30Independiente del VallevsFlamengoCopa LibertadoresFrank Pilantra1.90Frank Pilantra</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13. sep.TidTipEkspertOdds13:00Helsingør Vs SundbyCampoBet 3. DivisionBettingGuru1.58BettingGuru</t>
+          <t>13. sep.TidTipEkspertOdds13:00HelsingørvsSundbyCampoBet 3. DivisionBettingGuru1.58BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,43 +460,67 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13. sep.TidTipEkspertOdds13:00Næstved Vs ThistedCampoBet 2. DivisionBettingGuru1.98BettingGuru</t>
+          <t>13. sep.TidTipEkspertOdds13:00NæstvedvsThistedCampoBet 2. DivisionBettingGuru1.98BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>frank-pilantra</t>
+          <t>bettingguru</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11. sep.TidTipEkspertOdds02:30Independiente del VallevsFlamengoCopa LibertadoresFrank Pilantra1.55Frank Pilantra</t>
+          <t>12. sep.TidTipEkspertOdds19:00Zamalek Vs PortCAF, Champions LeagueBettingGuru1.78BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>frank-pilantra</t>
+          <t>loso</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12. sep.TidTipEkspertOdds23:30São PaulovsCorinthiansBrasileirãoFrank Pilantra1.45Frank Pilantra</t>
+          <t>11. sep.TidTipEkspertOdds19:00Over 2,5 målIFK KumlavsMotala AIFLoso1.70Loso</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>loso</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>11. sep.TidTipEkspertOdds19:00Over 4,5 målIFK KumlavsMotala AIFLoso5.00Loso</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>frank-pilantra</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>11. sep.TidTipEkspertOdds02:30Independiente del VallevsFlamengoCopa LibertadoresFrank Pilantra1.90Frank Pilantra</t>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>12. sep.TidTipEkspertOdds21:00Atletico MGvsFluminenseBrasileirãoFrank Pilantra1.60Frank Pilantra</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>12. sep.TidTipEkspertOdds23:30São PaulovsCorinthiansBrasileirãoFrank Pilantra1.45Frank Pilantra</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13. sep.TidTipEkspertOdds13:00NæstvedvsThistedCampoBet 2. DivisionBettingGuru1.98BettingGuru</t>
+          <t>12. sep.TidTipEkspertOdds19:00Zamalek Vs PortCAF, Champions LeagueBettingGuru1.78BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12. sep.TidTipEkspertOdds19:00Zamalek Vs PortCAF, Champions LeagueBettingGuru1.78BettingGuru</t>
+          <t>13. sep.TidTipEkspertOdds13:00NæstvedvsThistedCampoBet 2. DivisionBettingGuru1.98BettingGuru</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11. sep.TidTipEkspertOdds19:00Over 2,5 målIFK KumlavsMotala AIFLoso1.70Loso</t>
+          <t>11. sep.TidTipEkspertOdds19:00Over 4,5 målFC TrollhättanvsUtsiktens BKLoso3.45Loso</t>
         </is>
       </c>
     </row>
@@ -496,19 +496,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11. sep.TidTipEkspertOdds19:00Over 4,5 målIFK KumlavsMotala AIFLoso5.00Loso</t>
+          <t>11. sep.TidTipEkspertOdds19:00Over 2,5 målIFK KumlavsMotala AIFLoso1.70Loso</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>frank-pilantra</t>
+          <t>loso</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12. sep.TidTipEkspertOdds21:00Atletico MGvsFluminenseBrasileirãoFrank Pilantra1.60Frank Pilantra</t>
+          <t>11. sep.TidTipEkspertOdds19:00Over 4,5 målIFK KumlavsMotala AIFLoso5.00Loso</t>
         </is>
       </c>
     </row>
@@ -521,6 +521,18 @@
       <c r="B8" t="inlineStr">
         <is>
           <t>12. sep.TidTipEkspertOdds23:30São PaulovsCorinthiansBrasileirãoFrank Pilantra1.45Frank Pilantra</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>12. sep.TidTipEkspertOdds21:00Atletico MGvsFluminenseBrasileirãoFrank Pilantra1.60Frank Pilantra</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12. sep.TidTipEkspertOdds19:00Zamalek Vs PortCAF, Champions LeagueBettingGuru1.78BettingGuru</t>
+          <t>13. sep.TidTipEkspertOdds13:00NæstvedvsThistedCampoBet 2. DivisionBettingGuru1.98BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,65 +472,41 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13. sep.TidTipEkspertOdds13:00NæstvedvsThistedCampoBet 2. DivisionBettingGuru1.98BettingGuru</t>
+          <t>12. sep.TidTipEkspertOdds19:00Zamalek Vs PortCAF, Champions LeagueBettingGuru1.78BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>loso</t>
+          <t>frank-pilantra</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11. sep.TidTipEkspertOdds19:00Over 4,5 målFC TrollhättanvsUtsiktens BKLoso3.45Loso</t>
+          <t>12. sep.TidTipEkspertOdds23:30São PaulovsCorinthiansBrasileirãoFrank Pilantra1.45Frank Pilantra</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>loso</t>
+          <t>frank-pilantra</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11. sep.TidTipEkspertOdds19:00Over 2,5 målIFK KumlavsMotala AIFLoso1.70Loso</t>
+          <t>12. sep.TidTipEkspertOdds21:00GrêmiovsVasco da GamaBrasileirãoFrank Pilantra1.83Frank Pilantra</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>loso</t>
+          <t>frank-pilantra</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
-        <is>
-          <t>11. sep.TidTipEkspertOdds19:00Over 4,5 målIFK KumlavsMotala AIFLoso5.00Loso</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>12. sep.TidTipEkspertOdds23:30São PaulovsCorinthiansBrasileirãoFrank Pilantra1.45Frank Pilantra</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
         <is>
           <t>12. sep.TidTipEkspertOdds21:00Atletico MGvsFluminenseBrasileirãoFrank Pilantra1.60Frank Pilantra</t>
         </is>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13. sep.TidTipEkspertOdds13:00NæstvedvsThistedCampoBet 2. DivisionBettingGuru1.98BettingGuru</t>
+          <t>12. sep.TidTipEkspertOdds19:00Zamalek Vs PortCAF, Champions LeagueBettingGuru1.78BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,43 +472,103 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12. sep.TidTipEkspertOdds19:00Zamalek Vs PortCAF, Champions LeagueBettingGuru1.78BettingGuru</t>
+          <t>13. sep.TidTipEkspertOdds13:00NæstvedvsThistedCampoBet 2. DivisionBettingGuru1.98BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>frank-pilantra</t>
+          <t>loso</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12. sep.TidTipEkspertOdds23:30São PaulovsCorinthiansBrasileirãoFrank Pilantra1.45Frank Pilantra</t>
+          <t>12. sep.TidTipEkspertOdds14:00Kongahälla vinderKongahällavsAstrioLoso1.68Loso</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>frank-pilantra</t>
+          <t>loso</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12. sep.TidTipEkspertOdds21:00GrêmiovsVasco da GamaBrasileirãoFrank Pilantra1.83Frank Pilantra</t>
+          <t>12. sep.TidTipEkspertOdds16:00Over 3,25 målÅtvidabergs FFvsBK OlympicLoso1.87Loso</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>loso</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>12. sep.TidTipEkspertOdds15:00Over 4 mål (asian)FC RosengårdvsUppsalaLoso1.92Loso</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>loso</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>12. sep.TidTipEkspertOdds16:00Over 3,25 målStocksundvsKarlstadLoso1.85Loso</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>frank-pilantra</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>12. sep.TidTipEkspertOdds21:00GrêmiovsVasco da GamaBrasileirãoFrank Pilantra1.83Frank Pilantra</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>12. sep.TidTipEkspertOdds23:30PalmeirasvsSão PauloBrasileirãoFrank Pilantra1.57Frank Pilantra</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>12. sep.TidTipEkspertOdds21:00Atletico MGvsFluminenseBrasileirãoFrank Pilantra1.60Frank Pilantra</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12. sep.TidTipEkspertOdds23:30São PaulovsCorinthiansBrasileirãoFrank Pilantra1.45Frank Pilantra</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13. sep.TidTipEkspertOdds13:00HelsingørvsSundbyCampoBet 3. DivisionBettingGuru1.58BettingGuru</t>
+          <t>13. sep.TidTipEkspertOdds13:00NæstvedvsThistedCampoBet 2. DivisionBettingGuru1.98BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12. sep.TidTipEkspertOdds19:00Zamalek Vs PortCAF, Champions LeagueBettingGuru1.78BettingGuru</t>
+          <t>13. sep.TidTipEkspertOdds13:00HelsingørvsSundbyCampoBet 3. DivisionBettingGuru1.58BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,101 +472,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13. sep.TidTipEkspertOdds13:00NæstvedvsThistedCampoBet 2. DivisionBettingGuru1.98BettingGuru</t>
+          <t>17. sep.TidTipEkspertOdds00:00LDU Quito Vs PalmeirasCopa LibertadoresBettingGuru2.12BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>loso</t>
+          <t>frank-pilantra</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12. sep.TidTipEkspertOdds14:00Kongahälla vinderKongahällavsAstrioLoso1.68Loso</t>
+          <t>12. sep.TidTipEkspertOdds23:30PalmeirasvsSão PauloBrasileirãoFrank Pilantra1.57Frank Pilantra</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>loso</t>
+          <t>frank-pilantra</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
-        <is>
-          <t>12. sep.TidTipEkspertOdds16:00Over 3,25 målÅtvidabergs FFvsBK OlympicLoso1.87Loso</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>loso</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>12. sep.TidTipEkspertOdds15:00Over 4 mål (asian)FC RosengårdvsUppsalaLoso1.92Loso</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>loso</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>12. sep.TidTipEkspertOdds16:00Over 3,25 målStocksundvsKarlstadLoso1.85Loso</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>12. sep.TidTipEkspertOdds21:00GrêmiovsVasco da GamaBrasileirãoFrank Pilantra1.83Frank Pilantra</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>12. sep.TidTipEkspertOdds23:30PalmeirasvsSão PauloBrasileirãoFrank Pilantra1.57Frank Pilantra</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>12. sep.TidTipEkspertOdds21:00Atletico MGvsFluminenseBrasileirãoFrank Pilantra1.60Frank Pilantra</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
         <is>
           <t>12. sep.TidTipEkspertOdds23:30São PaulovsCorinthiansBrasileirãoFrank Pilantra1.45Frank Pilantra</t>
         </is>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -448,55 +448,55 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13. sep.TidTipEkspertOdds13:00NæstvedvsThistedCampoBet 2. DivisionBettingGuru1.98BettingGuru</t>
+          <t>17. sep.TidTipEkspertOdds00:00LDU Quito Vs PalmeirasCopa LibertadoresBettingGuru2.12BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>bettingguru</t>
+          <t>loso</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13. sep.TidTipEkspertOdds13:00HelsingørvsSundbyCampoBet 3. DivisionBettingGuru1.58BettingGuru</t>
+          <t>13. sep.TidTipEkspertOdds16:00Over 4,5 målÄngbyvsFrankeLoso3.75Loso</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bettingguru</t>
+          <t>loso</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>17. sep.TidTipEkspertOdds00:00LDU Quito Vs PalmeirasCopa LibertadoresBettingGuru2.12BettingGuru</t>
+          <t>13. sep.TidTipEkspertOdds15:00Over 5,5 målNorrköpingvsOddevoldLoso8.00Loso</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>frank-pilantra</t>
+          <t>loso</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12. sep.TidTipEkspertOdds23:30PalmeirasvsSão PauloBrasileirãoFrank Pilantra1.57Frank Pilantra</t>
+          <t>13. sep.TidTipEkspertOdds15:00Over 4,5 målAFC EskilstunavsPiteå IFLoso3.75Loso</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>frank-pilantra</t>
+          <t>loso</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12. sep.TidTipEkspertOdds23:30São PaulovsCorinthiansBrasileirãoFrank Pilantra1.45Frank Pilantra</t>
+          <t>13. sep.TidTipEkspertOdds14:00Over 5,5 målHammarbyvsBrommapojkarnaLoso5.25Loso</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,48 +455,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>loso</t>
+          <t>frank-pilantra</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13. sep.TidTipEkspertOdds16:00Over 4,5 målÄngbyvsFrankeLoso3.75Loso</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>loso</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>13. sep.TidTipEkspertOdds15:00Over 5,5 målNorrköpingvsOddevoldLoso8.00Loso</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>loso</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>13. sep.TidTipEkspertOdds15:00Over 4,5 målAFC EskilstunavsPiteå IFLoso3.75Loso</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>loso</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>13. sep.TidTipEkspertOdds14:00Over 5,5 målHammarbyvsBrommapojkarnaLoso5.25Loso</t>
+          <t>16. sep.TidTipEkspertOdds00:00PlatensevsFluminenseCopa LibertadoresFrank Pilantra1.62Frank Pilantra</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,6 +459,18 @@
         </is>
       </c>
       <c r="B3" t="inlineStr">
+        <is>
+          <t>16. sep.TidTipEkspertOdds02:30São PaulovsBoca JuniorsCopa SudamericanaFrank Pilantra1.75Frank Pilantra</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>16. sep.TidTipEkspertOdds00:00PlatensevsFluminenseCopa LibertadoresFrank Pilantra1.62Frank Pilantra</t>
         </is>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17. sep.TidTipEkspertOdds00:00LDU Quito Vs PalmeirasCopa LibertadoresBettingGuru2.12BettingGuru</t>
+          <t>17. sep.TidTipEkspertOdds00:00LDU QuitovsPalmeirasCopa LibertadoresBettingGuru2.12BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16. sep.TidTipEkspertOdds02:30São PaulovsBoca JuniorsCopa SudamericanaFrank Pilantra1.75Frank Pilantra</t>
+          <t>16. sep.TidTipEkspertOdds00:00PlatensevsFluminenseCopa LibertadoresFrank Pilantra1.62Frank Pilantra</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16. sep.TidTipEkspertOdds00:00PlatensevsFluminenseCopa LibertadoresFrank Pilantra1.62Frank Pilantra</t>
+          <t>16. sep.TidTipEkspertOdds02:30São PaulovsBoca JuniorsCopa SudamericanaFrank Pilantra1.75Frank Pilantra</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16. sep.TidTipEkspertOdds00:00PlatensevsFluminenseCopa LibertadoresFrank Pilantra1.62Frank Pilantra</t>
+          <t>17. sep.TidTipEkspertOdds02:30CorinthiansvsEstudiantesCopa LibertadoresFrank Pilantra1.57Frank Pilantra</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>16. sep.TidTipEkspertOdds00:00PlatensevsFluminenseCopa LibertadoresFrank Pilantra1.62Frank Pilantra</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>16. sep.TidTipEkspertOdds02:30São PaulovsBoca JuniorsCopa SudamericanaFrank Pilantra1.75Frank Pilantra</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>17. sep.TidTipEkspertOdds00:00Atletico MGvsSantosCopa SudamericanaFrank Pilantra1.96Frank Pilantra</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,43 +448,43 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17. sep.TidTipEkspertOdds00:00LDU QuitovsPalmeirasCopa LibertadoresBettingGuru2.12BettingGuru</t>
+          <t>16. sep.TidTipEkspertOdds16:30Hørsholm-UsserødvsAarhus FremadDBU PokalenBettingGuru2.03BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>frank-pilantra</t>
+          <t>bettingguru</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>17. sep.TidTipEkspertOdds02:30CorinthiansvsEstudiantesCopa LibertadoresFrank Pilantra1.57Frank Pilantra</t>
+          <t>17. sep.TidTipEkspertOdds00:00LDU QuitovsPalmeirasCopa LibertadoresBettingGuru2.12BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>frank-pilantra</t>
+          <t>bettingguru</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16. sep.TidTipEkspertOdds00:00PlatensevsFluminenseCopa LibertadoresFrank Pilantra1.62Frank Pilantra</t>
+          <t>18. sep.TidTipEkspertOdds02:30FlamengovsIndependiente Del ValleCopa LibertadoresBettingGuru1.97BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>frank-pilantra</t>
+          <t>loso</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16. sep.TidTipEkspertOdds02:30São PaulovsBoca JuniorsCopa SudamericanaFrank Pilantra1.75Frank Pilantra</t>
+          <t>16. sep.TidTipEkspertOdds19:00IFK Östersund vinderIFK ÖstersundvsGottneLoso1.78Loso</t>
         </is>
       </c>
     </row>
@@ -495,6 +495,42 @@
         </is>
       </c>
       <c r="B6" t="inlineStr">
+        <is>
+          <t>17. sep.TidTipEkspertOdds02:30CorinthiansvsEstudiantesCopa LibertadoresFrank Pilantra1.57Frank Pilantra</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>16. sep.TidTipEkspertOdds00:00PlatensevsFluminenseCopa LibertadoresFrank Pilantra1.62Frank Pilantra</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>16. sep.TidTipEkspertOdds02:30São PaulovsBoca JuniorsCopa SudamericanaFrank Pilantra1.75Frank Pilantra</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>17. sep.TidTipEkspertOdds00:00Atletico MGvsSantosCopa SudamericanaFrank Pilantra1.96Frank Pilantra</t>
         </is>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16. sep.TidTipEkspertOdds16:30Hørsholm-UsserødvsAarhus FremadDBU PokalenBettingGuru2.03BettingGuru</t>
+          <t>17. sep.TidTipEkspertOdds00:00LDU QuitovsPalmeirasCopa LibertadoresBettingGuru2.12BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>17. sep.TidTipEkspertOdds00:00LDU QuitovsPalmeirasCopa LibertadoresBettingGuru2.12BettingGuru</t>
+          <t>16. sep.TidTipEkspertOdds16:30Hørsholm-UsserødvsAarhus FremadDBU PokalenBettingGuru2.03BettingGuru</t>
         </is>
       </c>
     </row>
@@ -484,19 +484,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16. sep.TidTipEkspertOdds19:00IFK Östersund vinderIFK ÖstersundvsGottneLoso1.78Loso</t>
+          <t>16. sep.TidTipEkspertOdds19:00Piteå vinderPiteåvsUmeåLoso2.95Loso</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>frank-pilantra</t>
+          <t>loso</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17. sep.TidTipEkspertOdds02:30CorinthiansvsEstudiantesCopa LibertadoresFrank Pilantra1.57Frank Pilantra</t>
+          <t>16. sep.TidTipEkspertOdds19:00IFK Östersund vinderIFK ÖstersundvsGottneLoso1.78Loso</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16. sep.TidTipEkspertOdds00:00PlatensevsFluminenseCopa LibertadoresFrank Pilantra1.62Frank Pilantra</t>
+          <t>17. sep.TidTipEkspertOdds00:00Atletico MGvsSantosCopa SudamericanaFrank Pilantra1.96Frank Pilantra</t>
         </is>
       </c>
     </row>
@@ -520,19 +520,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16. sep.TidTipEkspertOdds02:30São PaulovsBoca JuniorsCopa SudamericanaFrank Pilantra1.75Frank Pilantra</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>17. sep.TidTipEkspertOdds00:00Atletico MGvsSantosCopa SudamericanaFrank Pilantra1.96Frank Pilantra</t>
+          <t>17. sep.TidTipEkspertOdds02:30CorinthiansvsEstudiantesCopa LibertadoresFrank Pilantra1.57Frank Pilantra</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17. sep.TidTipEkspertOdds00:00LDU QuitovsPalmeirasCopa LibertadoresBettingGuru2.12BettingGuru</t>
+          <t>19. sep.TidTipEkspertOdds23:30RemovsSantosBrasilien, Serie ABettingGuru2.17BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,67 +460,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16. sep.TidTipEkspertOdds16:30Hørsholm-UsserødvsAarhus FremadDBU PokalenBettingGuru2.03BettingGuru</t>
+          <t>18. sep.TidTipEkspertOdds02:30FlamengovsIndependiente Del ValleCopa LibertadoresBettingGuru1.97BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bettingguru</t>
+          <t>loso</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18. sep.TidTipEkspertOdds02:30FlamengovsIndependiente Del ValleCopa LibertadoresBettingGuru1.97BettingGuru</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>loso</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>16. sep.TidTipEkspertOdds19:00Piteå vinderPiteåvsUmeåLoso2.95Loso</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>loso</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>16. sep.TidTipEkspertOdds19:00IFK Östersund vinderIFK ÖstersundvsGottneLoso1.78Loso</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>17. sep.TidTipEkspertOdds00:00Atletico MGvsSantosCopa SudamericanaFrank Pilantra1.96Frank Pilantra</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>17. sep.TidTipEkspertOdds02:30CorinthiansvsEstudiantesCopa LibertadoresFrank Pilantra1.57Frank Pilantra</t>
+          <t>17. sep.TidTipEkspertOdds19:00Over 4,5 målVasalundvsHammarby TFFLoso4.33Loso</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>19. sep.TidTipEkspertOdds23:30RemovsSantosBrasilien, Serie ABettingGuru2.17BettingGuru</t>
+          <t>18. sep.TidTipEkspertOdds02:30FlamengovsIndependiente Del ValleCopa LibertadoresBettingGuru1.97BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,19 +460,31 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18. sep.TidTipEkspertOdds02:30FlamengovsIndependiente Del ValleCopa LibertadoresBettingGuru1.97BettingGuru</t>
+          <t>19. sep.TidTipEkspertOdds14:00Hørsholm-UsserødvsVanløse IFCampoBet 3. DivisionBettingGuru1.70BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>loso</t>
+          <t>bettingguru</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>17. sep.TidTipEkspertOdds19:00Over 4,5 målVasalundvsHammarby TFFLoso4.33Loso</t>
+          <t>19. sep.TidTipEkspertOdds23:30RemovsSantosBrasilien, Serie ABettingGuru2.17BettingGuru</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>bettingguru</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>18. sep.TidTipEkspertOdds19:00LyngbyvsSilkeborgSuperligaBettingGuru2.00BettingGuru</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>18. sep.TidTipEkspertOdds02:30FlamengovsIndependiente Del ValleCopa LibertadoresBettingGuru1.97BettingGuru</t>
+          <t>19. sep.TidTipEkspertOdds14:00Hørsholm-UsserødvsVanløse IFCampoBet 3. DivisionBettingGuru1.70BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,31 +460,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>19. sep.TidTipEkspertOdds14:00Hørsholm-UsserødvsVanløse IFCampoBet 3. DivisionBettingGuru1.70BettingGuru</t>
+          <t>19. sep.TidTipEkspertOdds23:30RemovsSantosBrasilien, Serie ABettingGuru2.17BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bettingguru</t>
+          <t>frank-pilantra</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>19. sep.TidTipEkspertOdds23:30RemovsSantosBrasilien, Serie ABettingGuru2.17BettingGuru</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>bettingguru</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>18. sep.TidTipEkspertOdds19:00LyngbyvsSilkeborgSuperligaBettingGuru2.00BettingGuru</t>
+          <t>19. sep.TidTipEkspertOdds22:00MirassolvsBotafogoBrasileirãoFrank Pilantra1.65Frank Pilantra</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>19. sep.TidTipEkspertOdds14:00Hørsholm-UsserødvsVanløse IFCampoBet 3. DivisionBettingGuru1.70BettingGuru</t>
+          <t>19. sep.TidTipEkspertOdds23:30RemovsSantosBrasilien, Serie ABettingGuru2.17BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,17 +460,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>19. sep.TidTipEkspertOdds23:30RemovsSantosBrasilien, Serie ABettingGuru2.17BettingGuru</t>
+          <t>19. sep.TidTipEkspertOdds14:00Hørsholm-UsserødvsVanløse IFCampoBet 3. DivisionBettingGuru1.70BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>loso</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>19. sep.TidTipEkspertOdds14:00Skara vinderSkaravsAhlaforsLoso2.30Loso</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>frank-pilantra</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>19. sep.TidTipEkspertOdds22:00MirassolvsBotafogoBrasileirãoFrank Pilantra1.65Frank Pilantra</t>
         </is>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>19. sep.TidTipEkspertOdds23:30RemovsSantosBrasilien, Serie ABettingGuru2.17BettingGuru</t>
+          <t>19. sep.TidTipEkspertOdds14:00Hørsholm-UsserødvsVanløse IFCampoBet 3. DivisionBettingGuru1.70BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>19. sep.TidTipEkspertOdds14:00Hørsholm-UsserødvsVanløse IFCampoBet 3. DivisionBettingGuru1.70BettingGuru</t>
+          <t>19. sep.TidTipEkspertOdds23:30RemovsSantosBrasilien, Serie ABettingGuru2.17BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,17 +472,41 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>19. sep.TidTipEkspertOdds14:00Skara vinderSkaravsAhlaforsLoso2.30Loso</t>
+          <t>19. sep.TidTipEkspertOdds16:00Over 4,5 målAFC MalmövsUtsiktens BKLoso3.25Loso</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>loso</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>19. sep.TidTipEkspertOdds14:00Skara vinderSkaravsAhlaforsLoso2.30Loso</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>loso</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>19. sep.TidTipEkspertOdds15:00Over 5,5 målHestraforsvsKongahällaLoso4.50Loso</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>frank-pilantra</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>19. sep.TidTipEkspertOdds22:00MirassolvsBotafogoBrasileirãoFrank Pilantra1.65Frank Pilantra</t>
         </is>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>19. sep.TidTipEkspertOdds14:00Hørsholm-UsserødvsVanløse IFCampoBet 3. DivisionBettingGuru1.70BettingGuru</t>
+          <t>19. sep.TidTipEkspertOdds23:30RemovsSantosBrasilien, Serie ABettingGuru2.17BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,53 +460,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>19. sep.TidTipEkspertOdds23:30RemovsSantosBrasilien, Serie ABettingGuru2.17BettingGuru</t>
+          <t>20. sep.TidTipEkspertOdds14:00Brøndby IF – Fc KøbenhavnSuperligaBettingGuru2.80BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>loso</t>
+          <t>frank-pilantra</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
-        <is>
-          <t>19. sep.TidTipEkspertOdds16:00Over 4,5 målAFC MalmövsUtsiktens BKLoso3.25Loso</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>loso</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>19. sep.TidTipEkspertOdds14:00Skara vinderSkaravsAhlaforsLoso2.30Loso</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>loso</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>19. sep.TidTipEkspertOdds15:00Over 5,5 målHestraforsvsKongahällaLoso4.50Loso</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
         <is>
           <t>19. sep.TidTipEkspertOdds22:00MirassolvsBotafogoBrasileirãoFrank Pilantra1.65Frank Pilantra</t>
         </is>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>19. sep.TidTipEkspertOdds23:30RemovsSantosBrasilien, Serie ABettingGuru2.17BettingGuru</t>
+          <t>22. sep.TidTipEkspertOdds07:00Vietnam U23vsUzbekistan U23Asian GamesBettingGuru3.30BettingGuru</t>
         </is>
       </c>
     </row>
@@ -461,18 +461,6 @@
       <c r="B3" t="inlineStr">
         <is>
           <t>20. sep.TidTipEkspertOdds14:00Brøndby IF – Fc KøbenhavnSuperligaBettingGuru2.80BettingGuru</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>19. sep.TidTipEkspertOdds22:00MirassolvsBotafogoBrasileirãoFrank Pilantra1.65Frank Pilantra</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>22. sep.TidTipEkspertOdds07:00Vietnam U23vsUzbekistan U23Asian GamesBettingGuru3.30BettingGuru</t>
+          <t>20. sep.TidTipEkspertOdds14:00Brøndby IF – Fc KøbenhavnSuperligaBettingGuru2.80BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20. sep.TidTipEkspertOdds14:00Brøndby IF – Fc KøbenhavnSuperligaBettingGuru2.80BettingGuru</t>
+          <t>22. sep.TidTipEkspertOdds07:00Vietnam U23vsUzbekistan U23Asian GamesBettingGuru3.30BettingGuru</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>loso</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>20. sep.TidTipEkspertOdds15:00Stocksund -0,5IFK StocksundvsUmeå FCLoso2.67Loso</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20. sep.TidTipEkspertOdds14:00Brøndby IF – Fc KøbenhavnSuperligaBettingGuru2.80BettingGuru</t>
+          <t>22. sep.TidTipEkspertOdds07:00Vietnam U23vsUzbekistan U23Asian GamesBettingGuru3.30BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,19 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>22. sep.TidTipEkspertOdds07:00Vietnam U23vsUzbekistan U23Asian GamesBettingGuru3.30BettingGuru</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>loso</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>20. sep.TidTipEkspertOdds15:00Stocksund -0,5IFK StocksundvsUmeå FCLoso2.67Loso</t>
+          <t>26. sep.TidTipEkspertOdds18:00IslandvsEstlandUEFA, Nations LeagueBettingGuru1.91BettingGuru</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>22. sep.TidTipEkspertOdds07:00Vietnam U23vsUzbekistan U23Asian GamesBettingGuru3.30BettingGuru</t>
+          <t>26. sep.TidTipEkspertOdds18:00IslandvsEstlandUEFA, Nations LeagueBettingGuru1.91BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>26. sep.TidTipEkspertOdds18:00IslandvsEstlandUEFA, Nations LeagueBettingGuru1.91BettingGuru</t>
+          <t>22. sep.TidTipEkspertOdds07:00Vietnam U23vsUzbekistan U23Asian GamesBettingGuru3.30BettingGuru</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,17 +460,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>22. sep.TidTipEkspertOdds07:00Vietnam U23vsUzbekistan U23Asian GamesBettingGuru3.30BettingGuru</t>
+          <t>25. sep.TidTipEkspertOdds18:00GambiavsSomaliaAFCON, KvalifikationenBettingGuru1.80BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>bettingguru</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>25. sep.TidTipEkspertOdds18:00NigeriavsMadagascarAFCON, KvalifikationenBettingGuru1.83BettingGuru</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>frank-pilantra</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
         </is>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>25. sep.TidTipEkspertOdds18:00GambiavsSomaliaAFCON, KvalifikationenBettingGuru1.80BettingGuru</t>
+          <t>25. sep.TidTipEkspertOdds18:00NigeriavsMadagascarAFCON, KvalifikationenBettingGuru1.83BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,17 +472,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>25. sep.TidTipEkspertOdds18:00NigeriavsMadagascarAFCON, KvalifikationenBettingGuru1.83BettingGuru</t>
+          <t>25. sep.TidTipEkspertOdds18:00GambiavsSomaliaAFCON, KvalifikationenBettingGuru1.80BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>loso</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>24. sep.TidTipEkspertOdds20:15Over 5,5 målKongahällavsLindomeLoso4.65Loso</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>frank-pilantra</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
         </is>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>25. sep.TidTipEkspertOdds18:00NigeriavsMadagascarAFCON, KvalifikationenBettingGuru1.83BettingGuru</t>
+          <t>27. sep.TidTipEkspertOdds21:00GuyanavsCaymanøerneCONCACAF, Nations LeagueBettingGuru1.75BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,29 +472,65 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>25. sep.TidTipEkspertOdds18:00GambiavsSomaliaAFCON, KvalifikationenBettingGuru1.80BettingGuru</t>
+          <t>27. sep.TidTipEkspertOdds21:00GuyanavsCaymanøerneCONCACAF, Nations LeagueBettingGuru1.88BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>loso</t>
+          <t>bettingguru</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24. sep.TidTipEkspertOdds20:15Over 5,5 målKongahällavsLindomeLoso4.65Loso</t>
+          <t>27. sep.TidTipEkspertOdds23:00AlianzavsInca ArubaEl Salvador, Primera DivisionBettingGuru1.94BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>loso</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>26. sep.TidTipEkspertOdds14:00Lidköping vinderKumlavsLidköpingLoso2.72Loso</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>loso</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>26. sep.TidTipEkspertOdds14:00Galtabäck -1 EHGaltabäckvsAstrioLoso2.45Loso</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>loso</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>26. sep.TidTipEkspertOdds18:00Olivier Nadeau scorer 2+ målVäxjö LakersvsHV 71Loso35.00Loso</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>frank-pilantra</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
         </is>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>26. sep.TidTipEkspertOdds18:00IslandvsEstlandUEFA, Nations LeagueBettingGuru1.91BettingGuru</t>
+          <t>27. sep.TidTipEkspertOdds21:00GuyanavsCaymanøerneCONCACAF, Nations LeagueBettingGuru1.75BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>27. sep.TidTipEkspertOdds21:00GuyanavsCaymanøerneCONCACAF, Nations LeagueBettingGuru1.75BettingGuru</t>
+          <t>27. sep.TidTipEkspertOdds21:00GuyanavsCaymanøerneCONCACAF, Nations LeagueBettingGuru1.88BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>27. sep.TidTipEkspertOdds21:00GuyanavsCaymanøerneCONCACAF, Nations LeagueBettingGuru1.88BettingGuru</t>
+          <t>27. sep.TidTipEkspertOdds23:00AlianzavsInca ArubaEl Salvador, Primera DivisionBettingGuru1.94BettingGuru</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27. sep.TidTipEkspertOdds23:00AlianzavsInca ArubaEl Salvador, Primera DivisionBettingGuru1.94BettingGuru</t>
+          <t>26. sep.TidTipEkspertOdds18:00IslandvsEstlandUEFA, Nations LeagueBettingGuru1.91BettingGuru</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26. sep.TidTipEkspertOdds14:00Lidköping vinderKumlavsLidköpingLoso2.72Loso</t>
+          <t>26. sep.TidTipEkspertOdds18:00Tarun Fizer scorerSödertäljevsOskarshamnLoso3.60Loso</t>
         </is>
       </c>
     </row>
@@ -508,29 +508,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26. sep.TidTipEkspertOdds14:00Galtabäck -1 EHGaltabäckvsAstrioLoso2.45Loso</t>
+          <t>26. sep.TidTipEkspertOdds18:00Olivier Nadeau scorer 2+ målVäxjö LakersvsHV 71Loso35.00Loso</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>loso</t>
+          <t>frank-pilantra</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
-        <is>
-          <t>26. sep.TidTipEkspertOdds18:00Olivier Nadeau scorer 2+ målVäxjö LakersvsHV 71Loso35.00Loso</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
         <is>
           <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
         </is>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>27. sep.TidTipEkspertOdds21:00GuyanavsCaymanøerneCONCACAF, Nations LeagueBettingGuru1.88BettingGuru</t>
+          <t>27. sep.TidTipEkspertOdds20:45IsraelvsIrlandUEFA, Nations LeagueBettingGuru1.75BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>27. sep.TidTipEkspertOdds23:00AlianzavsInca ArubaEl Salvador, Primera DivisionBettingGuru1.94BettingGuru</t>
+          <t>27. sep.TidTipEkspertOdds21:00GuyanavsCaymanøerneCONCACAF, Nations LeagueBettingGuru1.88BettingGuru</t>
         </is>
       </c>
     </row>
@@ -484,41 +484,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26. sep.TidTipEkspertOdds18:00IslandvsEstlandUEFA, Nations LeagueBettingGuru1.91BettingGuru</t>
+          <t>27. sep.TidTipEkspertOdds20:45IsraelvsIrlandUEFA, Nations LeagueBettingGuru2.15BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>loso</t>
+          <t>bettingguru</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26. sep.TidTipEkspertOdds18:00Tarun Fizer scorerSödertäljevsOskarshamnLoso3.60Loso</t>
+          <t>27. sep.TidTipEkspertOdds23:00AlianzavsInca ArubaEl Salvador, Primera DivisionBettingGuru1.94BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>loso</t>
+          <t>frank-pilantra</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
-        <is>
-          <t>26. sep.TidTipEkspertOdds18:00Olivier Nadeau scorer 2+ målVäxjö LakersvsHV 71Loso35.00Loso</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
         <is>
           <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
         </is>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>27. sep.TidTipEkspertOdds21:00GuyanavsCaymanøerneCONCACAF, Nations LeagueBettingGuru1.75BettingGuru</t>
+          <t>27. sep.TidTipEkspertOdds20:45IsraelvsIrlandUEFA, Nations LeagueBettingGuru1.75BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>27. sep.TidTipEkspertOdds20:45IsraelvsIrlandUEFA, Nations LeagueBettingGuru1.75BettingGuru</t>
+          <t>27. sep.TidTipEkspertOdds21:00GuyanavsCaymanøerneCONCACAF, Nations LeagueBettingGuru1.88BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>27. sep.TidTipEkspertOdds21:00GuyanavsCaymanøerneCONCACAF, Nations LeagueBettingGuru1.88BettingGuru</t>
+          <t>27. sep.TidTipEkspertOdds21:00GuyanavsCaymanøerneCONCACAF, Nations LeagueBettingGuru1.75BettingGuru</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27. sep.TidTipEkspertOdds20:45IsraelvsIrlandUEFA, Nations LeagueBettingGuru2.15BettingGuru</t>
+          <t>27. sep.TidTipEkspertOdds23:00AlianzavsInca ArubaEl Salvador, Primera DivisionBettingGuru1.94BettingGuru</t>
         </is>
       </c>
     </row>
@@ -496,17 +496,53 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>27. sep.TidTipEkspertOdds23:00AlianzavsInca ArubaEl Salvador, Primera DivisionBettingGuru1.94BettingGuru</t>
+          <t>27. sep.TidTipEkspertOdds20:45IsraelvsIrlandUEFA, Nations LeagueBettingGuru2.15BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>loso</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>27. sep.TidTipEkspertOdds13:00Eker Örebro -0,5LindövsEker ÖrebroLoso5.25Loso</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>loso</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>27. sep.TidTipEkspertOdds13:00Haninge over 4,5 målHaningevsSmedbyLoso7.00Loso</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>loso</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>27. sep.TidTipEkspertOdds16:00Gefle -0,5GeflevsVasalundLoso2.25Loso</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>frank-pilantra</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
         </is>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>27. sep.TidTipEkspertOdds20:45IsraelvsIrlandUEFA, Nations LeagueBettingGuru1.75BettingGuru</t>
+          <t>27. sep.TidTipEkspertOdds23:00AlianzavsInca ArubaEl Salvador, Primera DivisionBettingGuru1.94BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>27. sep.TidTipEkspertOdds21:00GuyanavsCaymanøerneCONCACAF, Nations LeagueBettingGuru1.88BettingGuru</t>
+          <t>28. sep.TidTipEkspertOdds20:45BelgienvsFrankrigUEFA, Nations LeagueBettingGuru1.80BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>27. sep.TidTipEkspertOdds21:00GuyanavsCaymanøerneCONCACAF, Nations LeagueBettingGuru1.75BettingGuru</t>
+          <t>27. sep.TidTipEkspertOdds21:00GuyanavsCaymanøerneCONCACAF, Nations LeagueBettingGuru1.88BettingGuru</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27. sep.TidTipEkspertOdds23:00AlianzavsInca ArubaEl Salvador, Primera DivisionBettingGuru1.94BettingGuru</t>
+          <t>27. sep.TidTipEkspertOdds21:00GuyanavsCaymanøerneCONCACAF, Nations LeagueBettingGuru1.75BettingGuru</t>
         </is>
       </c>
     </row>
@@ -496,43 +496,43 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>27. sep.TidTipEkspertOdds20:45IsraelvsIrlandUEFA, Nations LeagueBettingGuru2.15BettingGuru</t>
+          <t>28. sep.TidTipEkspertOdds16:00KirgisistanvsMaldiverneTræningskampBettingGuru1.60BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>loso</t>
+          <t>bettingguru</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>27. sep.TidTipEkspertOdds13:00Eker Örebro -0,5LindövsEker ÖrebroLoso5.25Loso</t>
+          <t>27. sep.TidTipEkspertOdds20:45IsraelvsIrlandUEFA, Nations LeagueBettingGuru1.75BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>loso</t>
+          <t>bettingguru</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>27. sep.TidTipEkspertOdds13:00Haninge over 4,5 målHaningevsSmedbyLoso7.00Loso</t>
+          <t>27. sep.TidTipEkspertOdds20:45IsraelvsIrlandUEFA, Nations LeagueBettingGuru2.15BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>loso</t>
+          <t>bettingguru</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>27. sep.TidTipEkspertOdds16:00Gefle -0,5GeflevsVasalundLoso2.25Loso</t>
+          <t>29. sep.TidTipEkspertOdds02:00Saint Kitts &amp; NevisvsGrenadaCONCACAF, Nations LeagueBettingGuru2.00BettingGuru</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>27. sep.TidTipEkspertOdds23:00AlianzavsInca ArubaEl Salvador, Primera DivisionBettingGuru1.94BettingGuru</t>
+          <t>28. sep.TidTipEkspertOdds20:45BelgienvsFrankrigUEFA, Nations LeagueBettingGuru1.80BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>28. sep.TidTipEkspertOdds20:45BelgienvsFrankrigUEFA, Nations LeagueBettingGuru1.80BettingGuru</t>
+          <t>28. sep.TidTipEkspertOdds16:00KirgisistanvsMaldiverneTræningskampBettingGuru1.60BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,77 +472,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>27. sep.TidTipEkspertOdds21:00GuyanavsCaymanøerneCONCACAF, Nations LeagueBettingGuru1.88BettingGuru</t>
+          <t>29. sep.TidTipEkspertOdds02:00Saint Kitts &amp; NevisvsGrenadaCONCACAF, Nations LeagueBettingGuru2.00BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>bettingguru</t>
+          <t>frank-pilantra</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27. sep.TidTipEkspertOdds21:00GuyanavsCaymanøerneCONCACAF, Nations LeagueBettingGuru1.75BettingGuru</t>
+          <t>29. sep.TidTipEkspertOdds12:00AustralienvsBrasilienVenskabskampFrank Pilantra1.91Frank Pilantra</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bettingguru</t>
+          <t>frank-pilantra</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
-        <is>
-          <t>28. sep.TidTipEkspertOdds16:00KirgisistanvsMaldiverneTræningskampBettingGuru1.60BettingGuru</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>bettingguru</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>27. sep.TidTipEkspertOdds20:45IsraelvsIrlandUEFA, Nations LeagueBettingGuru1.75BettingGuru</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>bettingguru</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>27. sep.TidTipEkspertOdds20:45IsraelvsIrlandUEFA, Nations LeagueBettingGuru2.15BettingGuru</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>bettingguru</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>29. sep.TidTipEkspertOdds02:00Saint Kitts &amp; NevisvsGrenadaCONCACAF, Nations LeagueBettingGuru2.00BettingGuru</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
         <is>
           <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
         </is>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>28. sep.TidTipEkspertOdds20:45BelgienvsFrankrigUEFA, Nations LeagueBettingGuru1.80BettingGuru</t>
+          <t>29. sep.TidTipEkspertOdds02:00Saint Kitts &amp; NevisvsGrenadaCONCACAF, Nations LeagueBettingGuru2.00BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>28. sep.TidTipEkspertOdds16:00KirgisistanvsMaldiverneTræningskampBettingGuru1.60BettingGuru</t>
+          <t>28. sep.TidTipEkspertOdds20:45BelgienvsFrankrigUEFA, Nations LeagueBettingGuru1.80BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,19 +472,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>29. sep.TidTipEkspertOdds02:00Saint Kitts &amp; NevisvsGrenadaCONCACAF, Nations LeagueBettingGuru2.00BettingGuru</t>
+          <t>29. sep.TidTipEkspertOdds20:45San MarinovsAlbanienUEFA, Nations LeagueBettingGuru2.05BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>frank-pilantra</t>
+          <t>bettingguru</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29. sep.TidTipEkspertOdds12:00AustralienvsBrasilienVenskabskampFrank Pilantra1.91Frank Pilantra</t>
+          <t>1. okt.TidTipEkspertOdds18:00AserbajdsjanvsLiechtensteinUEFA, Nations LeagueBettingGuru1.50BettingGuru</t>
         </is>
       </c>
     </row>
@@ -497,6 +497,18 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>29. sep.TidTipEkspertOdds12:00AustralienvsBrasilienVenskabskampFrank Pilantra1.91Frank Pilantra</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>29. sep.TidTipEkspertOdds02:00Saint Kitts &amp; NevisvsGrenadaCONCACAF, Nations LeagueBettingGuru2.00BettingGuru</t>
+          <t>1. okt.TidTipEkspertOdds01:00ArgentinavsBoliviaTræningskampBettingGuru1.60BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>28. sep.TidTipEkspertOdds20:45BelgienvsFrankrigUEFA, Nations LeagueBettingGuru1.80BettingGuru</t>
+          <t>3. okt.TidTipEkspertOdds13:00MiddelfartvsFA 2000CampoBet 2. DivisionBettingGuru1.66BettingGuru</t>
         </is>
       </c>
     </row>
@@ -484,29 +484,53 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1. okt.TidTipEkspertOdds18:00AserbajdsjanvsLiechtensteinUEFA, Nations LeagueBettingGuru1.50BettingGuru</t>
+          <t>29. sep.TidTipEkspertOdds20:45LuxembourgvsIslandUEFA, Nations LeagueBettingGuru1.83BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>frank-pilantra</t>
+          <t>bettingguru</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
+          <t>1. okt.TidTipEkspertOdds18:00AserbajdsjanvsLiechtensteinUEFA, Nations LeagueBettingGuru1.50BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>bettingguru</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>29. sep.TidTipEkspertOdds02:00Saint Kitts &amp; NevisvsGrenadaCONCACAF, Nations LeagueBettingGuru2.00BettingGuru</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>frank-pilantra</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>29. sep.TidTipEkspertOdds12:00AustralienvsBrasilienVenskabskampFrank Pilantra1.91Frank Pilantra</t>
         </is>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1. okt.TidTipEkspertOdds01:00ArgentinavsBoliviaTræningskampBettingGuru1.60BettingGuru</t>
+          <t>29. sep.TidTipEkspertOdds20:45LuxembourgvsIslandUEFA, Nations LeagueBettingGuru1.83BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3. okt.TidTipEkspertOdds13:00MiddelfartvsFA 2000CampoBet 2. DivisionBettingGuru1.66BettingGuru</t>
+          <t>1. okt.TidTipEkspertOdds18:00AserbajdsjanvsLiechtensteinUEFA, Nations LeagueBettingGuru1.50BettingGuru</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29. sep.TidTipEkspertOdds20:45LuxembourgvsIslandUEFA, Nations LeagueBettingGuru1.83BettingGuru</t>
+          <t>1. okt.TidTipEkspertOdds01:00ArgentinavsBoliviaTræningskampBettingGuru1.60BettingGuru</t>
         </is>
       </c>
     </row>
@@ -496,31 +496,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1. okt.TidTipEkspertOdds18:00AserbajdsjanvsLiechtensteinUEFA, Nations LeagueBettingGuru1.50BettingGuru</t>
+          <t>3. okt.TidTipEkspertOdds13:00MiddelfartvsFA 2000CampoBet 2. DivisionBettingGuru1.66BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bettingguru</t>
+          <t>loso</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>29. sep.TidTipEkspertOdds02:00Saint Kitts &amp; NevisvsGrenadaCONCACAF, Nations LeagueBettingGuru2.00BettingGuru</t>
+          <t>29. sep.TidTipEkspertOdds19:04Under 164,5 pointUmeåvsSödertäljeLoso1.88Loso</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>frank-pilantra</t>
+          <t>loso</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
+          <t>29. sep.TidTipEkspertOdds19:04Högsbo +14,5HögsbovsBoråsLoso1.83Loso</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>29. sep.TidTipEkspertOdds12:00AustralienvsBrasilienVenskabskampFrank Pilantra1.91Frank Pilantra</t>
+          <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>29. sep.TidTipEkspertOdds20:45LuxembourgvsIslandUEFA, Nations LeagueBettingGuru1.83BettingGuru</t>
+          <t>3. okt.TidTipEkspertOdds13:00MiddelfartvsFA 2000CampoBet 2. DivisionBettingGuru1.66BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1. okt.TidTipEkspertOdds18:00AserbajdsjanvsLiechtensteinUEFA, Nations LeagueBettingGuru1.50BettingGuru</t>
+          <t>11. okt.TidTipEkspertOdds18:00Fc MidtjyllandvsFc KøbenhavnSuperligaBettingGuru2.00BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>29. sep.TidTipEkspertOdds20:45San MarinovsAlbanienUEFA, Nations LeagueBettingGuru2.05BettingGuru</t>
+          <t>1. okt.TidTipEkspertOdds18:00AserbajdsjanvsLiechtensteinUEFA, Nations LeagueBettingGuru1.50BettingGuru</t>
         </is>
       </c>
     </row>
@@ -491,46 +491,10 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bettingguru</t>
+          <t>frank-pilantra</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
-        <is>
-          <t>3. okt.TidTipEkspertOdds13:00MiddelfartvsFA 2000CampoBet 2. DivisionBettingGuru1.66BettingGuru</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>loso</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>29. sep.TidTipEkspertOdds19:04Under 164,5 pointUmeåvsSödertäljeLoso1.88Loso</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>loso</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>29. sep.TidTipEkspertOdds19:04Högsbo +14,5HögsbovsBoråsLoso1.83Loso</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
         <is>
           <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
         </is>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3. okt.TidTipEkspertOdds13:00MiddelfartvsFA 2000CampoBet 2. DivisionBettingGuru1.66BettingGuru</t>
+          <t>1. okt.TidTipEkspertOdds18:00AserbajdsjanvsLiechtensteinUEFA, Nations LeagueBettingGuru1.50BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1. okt.TidTipEkspertOdds18:00AserbajdsjanvsLiechtensteinUEFA, Nations LeagueBettingGuru1.50BettingGuru</t>
+          <t>3. okt.TidTipEkspertOdds13:00MiddelfartvsFA 2000CampoBet 2. DivisionBettingGuru1.66BettingGuru</t>
         </is>
       </c>
     </row>
@@ -491,10 +491,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>bettingguru</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2. okt.TidTipEkspertOdds19:00Fremad AmagervsB93CampoBet 2. DivisionBettingGuru2.18BettingGuru</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>frank-pilantra</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
         </is>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1. okt.TidTipEkspertOdds18:00AserbajdsjanvsLiechtensteinUEFA, Nations LeagueBettingGuru1.50BettingGuru</t>
+          <t>3. okt.TidTipEkspertOdds13:00MiddelfartvsFA 2000CampoBet 2. DivisionBettingGuru1.66BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11. okt.TidTipEkspertOdds18:00Fc MidtjyllandvsFc KøbenhavnSuperligaBettingGuru2.00BettingGuru</t>
+          <t>3. okt.TidTipEkspertOdds14:00BrønshøjvsFremCampoBet 3. DivisionBettingGuru2.23BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3. okt.TidTipEkspertOdds13:00MiddelfartvsFA 2000CampoBet 2. DivisionBettingGuru1.66BettingGuru</t>
+          <t>1. okt.TidTipEkspertOdds18:00AserbajdsjanvsLiechtensteinUEFA, Nations LeagueBettingGuru1.50BettingGuru</t>
         </is>
       </c>
     </row>
@@ -503,10 +503,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>bettingguru</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>11. okt.TidTipEkspertOdds18:00Fc MidtjyllandvsFc KøbenhavnSuperligaBettingGuru2.00BettingGuru</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>frank-pilantra</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
         </is>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3. okt.TidTipEkspertOdds13:00MiddelfartvsFA 2000CampoBet 2. DivisionBettingGuru1.66BettingGuru</t>
+          <t>1. okt.TidTipEkspertOdds01:00ArgentinavsBoliviaTræningskampBettingGuru1.60BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3. okt.TidTipEkspertOdds14:00BrønshøjvsFremCampoBet 3. DivisionBettingGuru2.23BettingGuru</t>
+          <t>2. okt.TidTipEkspertOdds19:00Fremad AmagervsB93CampoBet 2. DivisionBettingGuru2.18BettingGuru</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1. okt.TidTipEkspertOdds01:00ArgentinavsBoliviaTræningskampBettingGuru1.60BettingGuru</t>
+          <t>3. okt.TidTipEkspertOdds14:00BrønshøjvsFremCampoBet 3. DivisionBettingGuru2.23BettingGuru</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2. okt.TidTipEkspertOdds19:00Fremad AmagervsB93CampoBet 2. DivisionBettingGuru2.18BettingGuru</t>
+          <t>11. okt.TidTipEkspertOdds18:00Fc MidtjyllandvsFc KøbenhavnSuperligaBettingGuru2.00BettingGuru</t>
         </is>
       </c>
     </row>
@@ -508,17 +508,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11. okt.TidTipEkspertOdds18:00Fc MidtjyllandvsFc KøbenhavnSuperligaBettingGuru2.00BettingGuru</t>
+          <t>3. okt.TidTipEkspertOdds13:00MiddelfartvsFA 2000CampoBet 2. DivisionBettingGuru1.66BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>loso</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1. okt.TidTipEkspertOdds19:00Skellefteå -1,5Skellefteå AIKvsMalmö RedhawksLoso1.81Loso</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>frank-pilantra</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
         </is>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1. okt.TidTipEkspertOdds01:00ArgentinavsBoliviaTræningskampBettingGuru1.60BettingGuru</t>
+          <t>2. okt.TidTipEkspertOdds23:00Saint Kitts &amp; NevisvsCubaCONCACAF, Nations LeagueBettingGuru3.60BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2. okt.TidTipEkspertOdds19:00Fremad AmagervsB93CampoBet 2. DivisionBettingGuru2.18BettingGuru</t>
+          <t>3. okt.TidTipEkspertOdds02:00BarbadosvsBermudaCONCACAF, Nations LeagueBettingGuru2.00BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1. okt.TidTipEkspertOdds18:00AserbajdsjanvsLiechtensteinUEFA, Nations LeagueBettingGuru1.50BettingGuru</t>
+          <t>2. okt.TidTipEkspertOdds19:00Fremad AmagervsB93CampoBet 2. DivisionBettingGuru2.18BettingGuru</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3. okt.TidTipEkspertOdds14:00BrønshøjvsFremCampoBet 3. DivisionBettingGuru2.23BettingGuru</t>
+          <t>3. okt.TidTipEkspertOdds13:00MiddelfartvsFA 2000CampoBet 2. DivisionBettingGuru1.66BettingGuru</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11. okt.TidTipEkspertOdds18:00Fc MidtjyllandvsFc KøbenhavnSuperligaBettingGuru2.00BettingGuru</t>
+          <t>3. okt.TidTipEkspertOdds14:00BrønshøjvsFremCampoBet 3. DivisionBettingGuru2.23BettingGuru</t>
         </is>
       </c>
     </row>
@@ -508,19 +508,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3. okt.TidTipEkspertOdds13:00MiddelfartvsFA 2000CampoBet 2. DivisionBettingGuru1.66BettingGuru</t>
+          <t>11. okt.TidTipEkspertOdds18:00Fc MidtjyllandvsFc KøbenhavnSuperligaBettingGuru2.00BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>loso</t>
+          <t>bettingguru</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1. okt.TidTipEkspertOdds19:00Skellefteå -1,5Skellefteå AIKvsMalmö RedhawksLoso1.81Loso</t>
+          <t>3. okt.TidTipEkspertOdds14:00NæsbyvsHolstebroCampoBet 3. DivisionBettingGuru1.81BettingGuru</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2. okt.TidTipEkspertOdds23:00Saint Kitts &amp; NevisvsCubaCONCACAF, Nations LeagueBettingGuru3.60BettingGuru</t>
+          <t>3. okt.TidTipEkspertOdds14:00BrønshøjvsFremCampoBet 3. DivisionBettingGuru2.23BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3. okt.TidTipEkspertOdds02:00BarbadosvsBermudaCONCACAF, Nations LeagueBettingGuru2.00BettingGuru</t>
+          <t>2. okt.TidTipEkspertOdds23:00Saint Kitts &amp; NevisvsCubaCONCACAF, Nations LeagueBettingGuru3.60BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2. okt.TidTipEkspertOdds19:00Fremad AmagervsB93CampoBet 2. DivisionBettingGuru2.18BettingGuru</t>
+          <t>3. okt.TidTipEkspertOdds14:00NæsbyvsHolstebroCampoBet 3. DivisionBettingGuru1.81BettingGuru</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3. okt.TidTipEkspertOdds13:00MiddelfartvsFA 2000CampoBet 2. DivisionBettingGuru1.66BettingGuru</t>
+          <t>3. okt.TidTipEkspertOdds02:00BarbadosvsBermudaCONCACAF, Nations LeagueBettingGuru2.00BettingGuru</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3. okt.TidTipEkspertOdds14:00BrønshøjvsFremCampoBet 3. DivisionBettingGuru2.23BettingGuru</t>
+          <t>11. okt.TidTipEkspertOdds18:00Fc MidtjyllandvsFc KøbenhavnSuperligaBettingGuru2.00BettingGuru</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11. okt.TidTipEkspertOdds18:00Fc MidtjyllandvsFc KøbenhavnSuperligaBettingGuru2.00BettingGuru</t>
+          <t>3. okt.TidTipEkspertOdds13:00MiddelfartvsFA 2000CampoBet 2. DivisionBettingGuru1.66BettingGuru</t>
         </is>
       </c>
     </row>
@@ -520,17 +520,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3. okt.TidTipEkspertOdds14:00NæsbyvsHolstebroCampoBet 3. DivisionBettingGuru1.81BettingGuru</t>
+          <t>2. okt.TidTipEkspertOdds19:00Fremad AmagervsB93CampoBet 2. DivisionBettingGuru2.18BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>loso</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2. okt.TidTipEkspertOdds19:04Over 170,5 pointBC LuleåvsSloga UppsalaLoso1.88Loso</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>frank-pilantra</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
         </is>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3. okt.TidTipEkspertOdds14:00BrønshøjvsFremCampoBet 3. DivisionBettingGuru2.23BettingGuru</t>
+          <t>4. okt.TidTipEkspertOdds20:45WalesvsDanmarkUEFA, Nations LeagueBettingGuru5.00BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2. okt.TidTipEkspertOdds23:00Saint Kitts &amp; NevisvsCubaCONCACAF, Nations LeagueBettingGuru3.60BettingGuru</t>
+          <t>11. okt.TidTipEkspertOdds18:00Fc MidtjyllandvsFc KøbenhavnSuperligaBettingGuru2.00BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3. okt.TidTipEkspertOdds14:00NæsbyvsHolstebroCampoBet 3. DivisionBettingGuru1.81BettingGuru</t>
+          <t>4. okt.TidTipEkspertOdds21:00GuyanavsDominicaCONCACAF, Nations LeagueBettingGuru2.00BettingGuru</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3. okt.TidTipEkspertOdds02:00BarbadosvsBermudaCONCACAF, Nations LeagueBettingGuru2.00BettingGuru</t>
+          <t>5. okt.TidTipEkspertOdds00:00Puerto RicovsCaymanøerneCONCACAF, Nations LeagueBettingGuru1.62BettingGuru</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11. okt.TidTipEkspertOdds18:00Fc MidtjyllandvsFc KøbenhavnSuperligaBettingGuru2.00BettingGuru</t>
+          <t>6. okt.TidTipEkspertOdds16:00KazakhstanvsFærøerneUEFA, Nations LeagueBettingGuru1.90BettingGuru</t>
         </is>
       </c>
     </row>
@@ -508,41 +508,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3. okt.TidTipEkspertOdds13:00MiddelfartvsFA 2000CampoBet 2. DivisionBettingGuru1.66BettingGuru</t>
+          <t>4. okt.TidTipEkspertOdds20:45IrlandvsIsraelUEFA, Nations LeagueBettingGuru1.72BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>bettingguru</t>
+          <t>frank-pilantra</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
-        <is>
-          <t>2. okt.TidTipEkspertOdds19:00Fremad AmagervsB93CampoBet 2. DivisionBettingGuru2.18BettingGuru</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>loso</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2. okt.TidTipEkspertOdds19:04Over 170,5 pointBC LuleåvsSloga UppsalaLoso1.88Loso</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
         <is>
           <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
         </is>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11. okt.TidTipEkspertOdds18:00Fc MidtjyllandvsFc KøbenhavnSuperligaBettingGuru2.00BettingGuru</t>
+          <t>4. okt.TidTipEkspertOdds20:45IrlandvsIsraelUEFA, Nations LeagueBettingGuru1.72BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4. okt.TidTipEkspertOdds21:00GuyanavsDominicaCONCACAF, Nations LeagueBettingGuru2.00BettingGuru</t>
+          <t>6. okt.TidTipEkspertOdds16:00KazakhstanvsFærøerneUEFA, Nations LeagueBettingGuru1.90BettingGuru</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5. okt.TidTipEkspertOdds00:00Puerto RicovsCaymanøerneCONCACAF, Nations LeagueBettingGuru1.62BettingGuru</t>
+          <t>11. okt.TidTipEkspertOdds18:00Fc MidtjyllandvsFc KøbenhavnSuperligaBettingGuru2.00BettingGuru</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6. okt.TidTipEkspertOdds16:00KazakhstanvsFærøerneUEFA, Nations LeagueBettingGuru1.90BettingGuru</t>
+          <t>4. okt.TidTipEkspertOdds21:00GuyanavsDominicaCONCACAF, Nations LeagueBettingGuru2.00BettingGuru</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4. okt.TidTipEkspertOdds20:45IrlandvsIsraelUEFA, Nations LeagueBettingGuru1.72BettingGuru</t>
+          <t>5. okt.TidTipEkspertOdds00:00Puerto RicovsCaymanøerneCONCACAF, Nations LeagueBettingGuru1.62BettingGuru</t>
         </is>
       </c>
     </row>
@@ -521,6 +521,18 @@
       <c r="B8" t="inlineStr">
         <is>
           <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>8. okt.TidTipEkspertOdds01:30BotafogovsVasco da GamaBrasileirãoFrank Pilantra1.66Frank Pilantra</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4. okt.TidTipEkspertOdds20:45WalesvsDanmarkUEFA, Nations LeagueBettingGuru5.00BettingGuru</t>
+          <t>5. okt.TidTipEkspertOdds00:00Puerto RicovsCaymanøerneCONCACAF, Nations LeagueBettingGuru1.62BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4. okt.TidTipEkspertOdds20:45IrlandvsIsraelUEFA, Nations LeagueBettingGuru1.72BettingGuru</t>
+          <t>11. okt.TidTipEkspertOdds18:00Fc MidtjyllandvsFc KøbenhavnSuperligaBettingGuru2.00BettingGuru</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11. okt.TidTipEkspertOdds18:00Fc MidtjyllandvsFc KøbenhavnSuperligaBettingGuru2.00BettingGuru</t>
+          <t>4. okt.TidTipEkspertOdds20:45IrlandvsIsraelUEFA, Nations LeagueBettingGuru1.72BettingGuru</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4. okt.TidTipEkspertOdds21:00GuyanavsDominicaCONCACAF, Nations LeagueBettingGuru2.00BettingGuru</t>
+          <t>7. okt.TidTipEkspertOdds01:00ArgentinavsBeninVenskabskampBettingGuru1.95BettingGuru</t>
         </is>
       </c>
     </row>
@@ -508,31 +508,79 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5. okt.TidTipEkspertOdds00:00Puerto RicovsCaymanøerneCONCACAF, Nations LeagueBettingGuru1.62BettingGuru</t>
+          <t>4. okt.TidTipEkspertOdds20:45WalesvsDanmarkUEFA, Nations LeagueBettingGuru5.00BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>frank-pilantra</t>
+          <t>bettingguru</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
+          <t>4. okt.TidTipEkspertOdds21:00GuyanavsDominicaCONCACAF, Nations LeagueBettingGuru2.00BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>bettingguru</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>7. okt.TidTipEkspertOdds01:00ArgentinavsBeninVenskabskampBettingGuru2.05BettingGuru</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>loso</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>4. okt.TidTipEkspertOdds14:00Kalix vinderKalixvsBorlängeLoso2.14Loso</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>loso</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>4. okt.TidTipEkspertOdds14:00Over 4,5 målAhlaforsvsMotalaLoso3.75Loso</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>frank-pilantra</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>8. okt.TidTipEkspertOdds01:30BotafogovsVasco da GamaBrasileirãoFrank Pilantra1.66Frank Pilantra</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5. okt.TidTipEkspertOdds00:00Puerto RicovsCaymanøerneCONCACAF, Nations LeagueBettingGuru1.62BettingGuru</t>
+          <t>7. okt.TidTipEkspertOdds01:00ArgentinavsBeninVenskabskampBettingGuru2.05BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6. okt.TidTipEkspertOdds16:00KazakhstanvsFærøerneUEFA, Nations LeagueBettingGuru1.90BettingGuru</t>
+          <t>7. okt.TidTipEkspertOdds01:00ArgentinavsBeninVenskabskampBettingGuru1.95BettingGuru</t>
         </is>
       </c>
     </row>
@@ -484,101 +484,41 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4. okt.TidTipEkspertOdds20:45IrlandvsIsraelUEFA, Nations LeagueBettingGuru1.72BettingGuru</t>
+          <t>6. okt.TidTipEkspertOdds16:00KazakhstanvsFærøerneUEFA, Nations LeagueBettingGuru1.90BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bettingguru</t>
+          <t>loso</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7. okt.TidTipEkspertOdds01:00ArgentinavsBeninVenskabskampBettingGuru1.95BettingGuru</t>
+          <t>5. okt.TidTipEkspertOdds19:00Grebbestad over 2,5 målHerrestads AIFvsGrebbestads IFLoso3.75Loso</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bettingguru</t>
+          <t>frank-pilantra</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4. okt.TidTipEkspertOdds20:45WalesvsDanmarkUEFA, Nations LeagueBettingGuru5.00BettingGuru</t>
+          <t>8. okt.TidTipEkspertOdds01:30BotafogovsVasco da GamaBrasileirãoFrank Pilantra1.66Frank Pilantra</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>bettingguru</t>
+          <t>frank-pilantra</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
-        <is>
-          <t>4. okt.TidTipEkspertOdds21:00GuyanavsDominicaCONCACAF, Nations LeagueBettingGuru2.00BettingGuru</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>bettingguru</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>7. okt.TidTipEkspertOdds01:00ArgentinavsBeninVenskabskampBettingGuru2.05BettingGuru</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>loso</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>4. okt.TidTipEkspertOdds14:00Kalix vinderKalixvsBorlängeLoso2.14Loso</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>loso</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>4. okt.TidTipEkspertOdds14:00Over 4,5 målAhlaforsvsMotalaLoso3.75Loso</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>8. okt.TidTipEkspertOdds01:30BotafogovsVasco da GamaBrasileirãoFrank Pilantra1.66Frank Pilantra</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
         <is>
           <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
         </is>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7. okt.TidTipEkspertOdds01:00ArgentinavsBeninVenskabskampBettingGuru2.05BettingGuru</t>
+          <t>7. okt.TidTipEkspertOdds01:00ArgentinavsBeninVenskabskampBettingGuru1.95BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11. okt.TidTipEkspertOdds18:00Fc MidtjyllandvsFc KøbenhavnSuperligaBettingGuru2.00BettingGuru</t>
+          <t>11. okt.TidTipEkspertOdds18:00FC MidtjyllandvsFC KøbenhavnSuperligaBettingGuru2.00BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7. okt.TidTipEkspertOdds01:00ArgentinavsBeninVenskabskampBettingGuru1.95BettingGuru</t>
+          <t>7. okt.TidTipEkspertOdds01:00ArgentinavsBeninVenskabskampBettingGuru2.05BettingGuru</t>
         </is>
       </c>
     </row>
@@ -491,12 +491,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>loso</t>
+          <t>frank-pilantra</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5. okt.TidTipEkspertOdds19:00Grebbestad over 2,5 målHerrestads AIFvsGrebbestads IFLoso3.75Loso</t>
+          <t>8. okt.TidTipEkspertOdds01:30BotafogovsVasco da GamaBrasileirãoFrank Pilantra1.66Frank Pilantra</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8. okt.TidTipEkspertOdds01:30BotafogovsVasco da GamaBrasileirãoFrank Pilantra1.66Frank Pilantra</t>
+          <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
+          <t>9. okt.TidTipEkspertOdds00:30Santos vc FlamengoBrasileirãoFrank Pilantra1.67Frank Pilantra</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7. okt.TidTipEkspertOdds01:00ArgentinavsBeninVenskabskampBettingGuru1.95BettingGuru</t>
+          <t>15. okt.TidTipEkspertOdds18:45GentvsAGFUEFA, Conference LeagueBettingGuru1.72BettingGuru</t>
         </is>
       </c>
     </row>
@@ -467,24 +467,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bettingguru</t>
+          <t>frank-pilantra</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7. okt.TidTipEkspertOdds01:00ArgentinavsBeninVenskabskampBettingGuru2.05BettingGuru</t>
+          <t>8. okt.TidTipEkspertOdds01:30BotafogovsVasco da GamaBrasileirãoFrank Pilantra1.66Frank Pilantra</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>bettingguru</t>
+          <t>frank-pilantra</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6. okt.TidTipEkspertOdds16:00KazakhstanvsFærøerneUEFA, Nations LeagueBettingGuru1.90BettingGuru</t>
+          <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
         </is>
       </c>
     </row>
@@ -495,30 +495,6 @@
         </is>
       </c>
       <c r="B6" t="inlineStr">
-        <is>
-          <t>8. okt.TidTipEkspertOdds01:30BotafogovsVasco da GamaBrasileirãoFrank Pilantra1.66Frank Pilantra</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
         <is>
           <t>9. okt.TidTipEkspertOdds00:30Santos vc FlamengoBrasileirãoFrank Pilantra1.67Frank Pilantra</t>
         </is>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15. okt.TidTipEkspertOdds18:45GentvsAGFUEFA, Conference LeagueBettingGuru1.72BettingGuru</t>
+          <t>11. okt.TidTipEkspertOdds18:00FC MidtjyllandvsFC KøbenhavnSuperligaBettingGuru2.00BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11. okt.TidTipEkspertOdds18:00FC MidtjyllandvsFC KøbenhavnSuperligaBettingGuru2.00BettingGuru</t>
+          <t>15. okt.TidTipEkspertOdds18:45GentvsAGFUEFA, Conference LeagueBettingGuru1.72BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>8. okt.TidTipEkspertOdds01:30BotafogovsVasco da GamaBrasileirãoFrank Pilantra1.66Frank Pilantra</t>
+          <t>9. okt.TidTipEkspertOdds00:30Santos vc FlamengoBrasileirãoFrank Pilantra1.67Frank Pilantra</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9. okt.TidTipEkspertOdds00:30Santos vc FlamengoBrasileirãoFrank Pilantra1.67Frank Pilantra</t>
+          <t>9. okt.TidTipEkspertOdds01:00Athletico PRvsAtletico MGBrasileirãoFrank Pilantra1.80Frank Pilantra</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,12 +467,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>frank-pilantra</t>
+          <t>bettingguru</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>9. okt.TidTipEkspertOdds00:30Santos vc FlamengoBrasileirãoFrank Pilantra1.67Frank Pilantra</t>
+          <t>11. okt.TidTipEkspertOdds20:45CagliarivsJuventusItalien, Serie ABettingGuru4.00BettingGuru</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
+          <t>9. okt.TidTipEkspertOdds01:00Athletico PRvsAtletico MGBrasileirãoFrank Pilantra1.80Frank Pilantra</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9. okt.TidTipEkspertOdds01:00Athletico PRvsAtletico MGBrasileirãoFrank Pilantra1.80Frank Pilantra</t>
+          <t>9. okt.TidTipEkspertOdds00:30Santos vc FlamengoBrasileirãoFrank Pilantra1.67Frank Pilantra</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15. okt.TidTipEkspertOdds18:45GentvsAGFUEFA, Conference LeagueBettingGuru1.72BettingGuru</t>
+          <t>11. okt.TidTipEkspertOdds15:00Crystal PalacevsNottingham ForestEngland, Premier LeagueBettingGuru1.95BettingGuru</t>
         </is>
       </c>
     </row>
@@ -479,34 +479,46 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>frank-pilantra</t>
+          <t>bettingguru</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9. okt.TidTipEkspertOdds01:00Athletico PRvsAtletico MGBrasileirãoFrank Pilantra1.80Frank Pilantra</t>
+          <t>15. okt.TidTipEkspertOdds18:45GentvsAGFUEFA, Conference LeagueBettingGuru1.72BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>frank-pilantra</t>
+          <t>loso</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9. okt.TidTipEkspertOdds00:30Santos vc FlamengoBrasileirãoFrank Pilantra1.67Frank Pilantra</t>
+          <t>9. okt.TidTipEkspertOdds18:00Under 163,5 pointNorrköpingvsSödertäljeLoso1.84Loso</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>loso</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>9. okt.TidTipEkspertOdds19:30Over 4,5 målLindomevsBöljanLoso3.45Loso</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>frank-pilantra</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
         </is>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11. okt.TidTipEkspertOdds18:00FC MidtjyllandvsFC KøbenhavnSuperligaBettingGuru2.00BettingGuru</t>
+          <t>11. okt.TidTipEkspertOdds20:45CagliarivsJuventusItalien, Serie ABettingGuru4.00BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11. okt.TidTipEkspertOdds20:45CagliarivsJuventusItalien, Serie ABettingGuru4.00BettingGuru</t>
+          <t>10. okt.TidTipEkspertOdds14:00Vanløse IFvsHolbæk B&amp;IDanmark, CampoBet 3. DivisionBettingGuru1.90BettingGuru</t>
         </is>
       </c>
     </row>
@@ -484,19 +484,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15. okt.TidTipEkspertOdds18:45GentvsAGFUEFA, Conference LeagueBettingGuru1.72BettingGuru</t>
+          <t>11. okt.TidTipEkspertOdds18:00FC MidtjyllandvsFC KøbenhavnSuperligaBettingGuru2.00BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>loso</t>
+          <t>bettingguru</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9. okt.TidTipEkspertOdds18:00Under 163,5 pointNorrköpingvsSödertäljeLoso1.84Loso</t>
+          <t>15. okt.TidTipEkspertOdds18:45GentvsAGFUEFA, Conference LeagueBettingGuru1.72BettingGuru</t>
         </is>
       </c>
     </row>
@@ -519,6 +519,18 @@
         </is>
       </c>
       <c r="B8" t="inlineStr">
+        <is>
+          <t>11. okt.TidTipEkspertOdds02:00São PaulovsVitoriaBrasileirãoFrank Pilantra1.57Frank Pilantra</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
         </is>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11. okt.TidTipEkspertOdds20:45CagliarivsJuventusItalien, Serie ABettingGuru4.00BettingGuru</t>
+          <t>15. okt.TidTipEkspertOdds18:45GentvsAGFUEFA, Conference LeagueBettingGuru1.72BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11. okt.TidTipEkspertOdds15:00Crystal PalacevsNottingham ForestEngland, Premier LeagueBettingGuru1.95BettingGuru</t>
+          <t>11. okt.TidTipEkspertOdds20:45CagliarivsJuventusItalien, Serie ABettingGuru4.00BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10. okt.TidTipEkspertOdds14:00Vanløse IFvsHolbæk B&amp;IDanmark, CampoBet 3. DivisionBettingGuru1.90BettingGuru</t>
+          <t>11. okt.TidTipEkspertOdds15:00Crystal PalacevsNottingham ForestEngland, Premier LeagueBettingGuru1.95BettingGuru</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11. okt.TidTipEkspertOdds18:00FC MidtjyllandvsFC KøbenhavnSuperligaBettingGuru2.00BettingGuru</t>
+          <t>10. okt.TidTipEkspertOdds14:00Vanløse IFvsHolbæk B&amp;IDanmark, CampoBet 3. DivisionBettingGuru1.90BettingGuru</t>
         </is>
       </c>
     </row>
@@ -496,43 +496,79 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15. okt.TidTipEkspertOdds18:45GentvsAGFUEFA, Conference LeagueBettingGuru1.72BettingGuru</t>
+          <t>18. okt.TidTipEkspertOdds00:30Athletico PRvsPalmeirasBrasilien, Serie ABettingGuru1.84BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>loso</t>
+          <t>bettingguru</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>9. okt.TidTipEkspertOdds19:30Over 4,5 målLindomevsBöljanLoso3.45Loso</t>
+          <t>11. okt.TidTipEkspertOdds18:00FC MidtjyllandvsFC KøbenhavnSuperligaBettingGuru2.00BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>frank-pilantra</t>
+          <t>loso</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11. okt.TidTipEkspertOdds02:00São PaulovsVitoriaBrasileirãoFrank Pilantra1.57Frank Pilantra</t>
+          <t>10. okt.TidTipEkspertOdds16:00Over 5,5 målFrankevsHelges IFLoso5.00Loso</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>loso</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>10. okt.TidTipEkspertOdds16:00Over 4,5 målTäbyvsLidingöLoso3.40Loso</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>loso</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>10. okt.TidTipEkspertOdds16:00Over 4,5 målKarlstadvsArlandaLoso4.65Loso</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>frank-pilantra</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11. okt.TidTipEkspertOdds02:00São PaulovsVitoriaBrasileirãoFrank Pilantra1.57Frank Pilantra</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15. okt.TidTipEkspertOdds18:45GentvsAGFUEFA, Conference LeagueBettingGuru1.72BettingGuru</t>
+          <t>11. okt.TidTipEkspertOdds18:00FC MidtjyllandvsFC KøbenhavnSuperligaBettingGuru2.00BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11. okt.TidTipEkspertOdds20:45CagliarivsJuventusItalien, Serie ABettingGuru4.00BettingGuru</t>
+          <t>18. okt.TidTipEkspertOdds00:30Athletico PRvsPalmeirasBrasilien, Serie ABettingGuru1.84BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11. okt.TidTipEkspertOdds15:00Crystal PalacevsNottingham ForestEngland, Premier LeagueBettingGuru1.95BettingGuru</t>
+          <t>11. okt.TidTipEkspertOdds20:45CagliarivsJuventusItalien, Serie ABettingGuru4.00BettingGuru</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10. okt.TidTipEkspertOdds14:00Vanløse IFvsHolbæk B&amp;IDanmark, CampoBet 3. DivisionBettingGuru1.90BettingGuru</t>
+          <t>15. okt.TidTipEkspertOdds18:45GentvsAGFUEFA, Conference LeagueBettingGuru1.72BettingGuru</t>
         </is>
       </c>
     </row>
@@ -496,79 +496,43 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18. okt.TidTipEkspertOdds00:30Athletico PRvsPalmeirasBrasilien, Serie ABettingGuru1.84BettingGuru</t>
+          <t>11. okt.TidTipEkspertOdds15:00Crystal PalacevsNottingham ForestEngland, Premier LeagueBettingGuru1.95BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bettingguru</t>
+          <t>frank-pilantra</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11. okt.TidTipEkspertOdds18:00FC MidtjyllandvsFC KøbenhavnSuperligaBettingGuru2.00BettingGuru</t>
+          <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>loso</t>
+          <t>frank-pilantra</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10. okt.TidTipEkspertOdds16:00Over 5,5 målFrankevsHelges IFLoso5.00Loso</t>
+          <t>11. okt.TidTipEkspertOdds02:00São PaulovsVitoriaBrasileirãoFrank Pilantra1.57Frank Pilantra</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>loso</t>
+          <t>frank-pilantra</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10. okt.TidTipEkspertOdds16:00Over 4,5 målTäbyvsLidingöLoso3.40Loso</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>loso</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>10. okt.TidTipEkspertOdds16:00Over 4,5 målKarlstadvsArlandaLoso4.65Loso</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>11. okt.TidTipEkspertOdds02:00São PaulovsVitoriaBrasileirãoFrank Pilantra1.57Frank Pilantra</t>
+          <t>11. okt.TidTipEkspertOdds21:00Atletico MGvsSantosBrasileirãoFrank Pilantra1.78Frank Pilantra</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11. okt.TidTipEkspertOdds18:00FC MidtjyllandvsFC KøbenhavnSuperligaBettingGuru2.00BettingGuru</t>
+          <t>11. okt.TidTipEkspertOdds15:00Crystal PalacevsNottingham ForestEngland, Premier LeagueBettingGuru1.95BettingGuru</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15. okt.TidTipEkspertOdds18:45GentvsAGFUEFA, Conference LeagueBettingGuru1.72BettingGuru</t>
+          <t>11. okt.TidTipEkspertOdds18:00FC MidtjyllandvsFC KøbenhavnSuperligaBettingGuru2.00BettingGuru</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11. okt.TidTipEkspertOdds15:00Crystal PalacevsNottingham ForestEngland, Premier LeagueBettingGuru1.95BettingGuru</t>
+          <t>15. okt.TidTipEkspertOdds18:45GentvsAGFUEFA, Conference LeagueBettingGuru1.72BettingGuru</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11. okt.TidTipEkspertOdds02:00São PaulovsVitoriaBrasileirãoFrank Pilantra1.57Frank Pilantra</t>
+          <t>11. okt.TidTipEkspertOdds22:30FlamengovsFluminenseBrasileirãoFrank Pilantra2.10Frank Pilantra</t>
         </is>
       </c>
     </row>
@@ -531,6 +531,30 @@
         </is>
       </c>
       <c r="B9" t="inlineStr">
+        <is>
+          <t>11. okt.TidTipEkspertOdds22:30GrêmiovsInternacionalBrasileirãoFrank Pilantra1.47Frank Pilantra</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>11. okt.TidTipEkspertOdds02:00São PaulovsVitoriaBrasileirãoFrank Pilantra1.57Frank Pilantra</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>11. okt.TidTipEkspertOdds21:00Atletico MGvsSantosBrasileirãoFrank Pilantra1.78Frank Pilantra</t>
         </is>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11. okt.TidTipEkspertOdds15:00Crystal PalacevsNottingham ForestEngland, Premier LeagueBettingGuru1.95BettingGuru</t>
+          <t>11. okt.TidTipEkspertOdds18:00FC MidtjyllandvsFC KøbenhavnSuperligaBettingGuru2.00BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18. okt.TidTipEkspertOdds00:30Athletico PRvsPalmeirasBrasilien, Serie ABettingGuru1.84BettingGuru</t>
+          <t>11. okt.TidTipEkspertOdds15:00Crystal PalacevsNottingham ForestEngland, Premier LeagueBettingGuru1.95BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11. okt.TidTipEkspertOdds20:45CagliarivsJuventusItalien, Serie ABettingGuru4.00BettingGuru</t>
+          <t>15. okt.TidTipEkspertOdds18:45GentvsAGFUEFA, Conference LeagueBettingGuru1.72BettingGuru</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11. okt.TidTipEkspertOdds18:00FC MidtjyllandvsFC KøbenhavnSuperligaBettingGuru2.00BettingGuru</t>
+          <t>11. okt.TidTipEkspertOdds20:45CagliarivsJuventusItalien, Serie ABettingGuru4.00BettingGuru</t>
         </is>
       </c>
     </row>
@@ -496,19 +496,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15. okt.TidTipEkspertOdds18:45GentvsAGFUEFA, Conference LeagueBettingGuru1.72BettingGuru</t>
+          <t>18. okt.TidTipEkspertOdds00:30Athletico PRvsPalmeirasBrasilien, Serie ABettingGuru1.84BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>frank-pilantra</t>
+          <t>loso</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
+          <t>11. okt.TidTipEkspertOdds16:00Visby Ladies +27,5Visby LadiesvsNorrköping DolphinsLoso1.83Loso</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11. okt.TidTipEkspertOdds22:30GrêmiovsInternacionalBrasileirãoFrank Pilantra1.47Frank Pilantra</t>
+          <t>11. okt.TidTipEkspertOdds21:00Atletico MGvsSantosBrasileirãoFrank Pilantra1.78Frank Pilantra</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11. okt.TidTipEkspertOdds02:00São PaulovsVitoriaBrasileirãoFrank Pilantra1.57Frank Pilantra</t>
+          <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11. okt.TidTipEkspertOdds21:00Atletico MGvsSantosBrasileirãoFrank Pilantra1.78Frank Pilantra</t>
+          <t>11. okt.TidTipEkspertOdds22:30GrêmiovsInternacionalBrasileirãoFrank Pilantra1.47Frank Pilantra</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11. okt.TidTipEkspertOdds18:00FC MidtjyllandvsFC KøbenhavnSuperligaBettingGuru2.00BettingGuru</t>
+          <t>13. okt.TidTipEkspertOdds18:45Sabah BakuvsSparta PragChampions LeagueBettingGuru1.84BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11. okt.TidTipEkspertOdds15:00Crystal PalacevsNottingham ForestEngland, Premier LeagueBettingGuru1.95BettingGuru</t>
+          <t>18. okt.TidTipEkspertOdds00:30Athletico PRvsPalmeirasBrasilien, Serie ABettingGuru1.84BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15. okt.TidTipEkspertOdds18:45GentvsAGFUEFA, Conference LeagueBettingGuru1.72BettingGuru</t>
+          <t>15. okt.TidTipEkspertOdds18:45PanathinaikosvsBorac Banja LukaConference LeagueBettingGuru2.00BettingGuru</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11. okt.TidTipEkspertOdds20:45CagliarivsJuventusItalien, Serie ABettingGuru4.00BettingGuru</t>
+          <t>15. okt.TidTipEkspertOdds18:45GentvsAGFUEFA, Conference LeagueBettingGuru1.72BettingGuru</t>
         </is>
       </c>
     </row>
@@ -496,19 +496,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18. okt.TidTipEkspertOdds00:30Athletico PRvsPalmeirasBrasilien, Serie ABettingGuru1.84BettingGuru</t>
+          <t>14. okt.TidTipEkspertOdds21:00Shakhtar DonetskvsAEK AthenChampions LeagueBettingGuru3.60BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>loso</t>
+          <t>frank-pilantra</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11. okt.TidTipEkspertOdds16:00Visby Ladies +27,5Visby LadiesvsNorrköping DolphinsLoso1.83Loso</t>
+          <t>11. okt.TidTipEkspertOdds22:30GrêmiovsInternacionalBrasileirãoFrank Pilantra1.47Frank Pilantra</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11. okt.TidTipEkspertOdds22:30FlamengovsFluminenseBrasileirãoFrank Pilantra2.10Frank Pilantra</t>
+          <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
         </is>
       </c>
     </row>
@@ -532,31 +532,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11. okt.TidTipEkspertOdds21:00Atletico MGvsSantosBrasileirãoFrank Pilantra1.78Frank Pilantra</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>11. okt.TidTipEkspertOdds22:30GrêmiovsInternacionalBrasileirãoFrank Pilantra1.47Frank Pilantra</t>
+          <t>11. okt.TidTipEkspertOdds22:30FlamengovsFluminenseBrasileirãoFrank Pilantra2.10Frank Pilantra</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13. okt.TidTipEkspertOdds18:45Sabah BakuvsSparta PragChampions LeagueBettingGuru1.84BettingGuru</t>
+          <t>15. okt.TidTipEkspertOdds18:45GentvsAGFUEFA, Conference LeagueBettingGuru1.72BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18. okt.TidTipEkspertOdds00:30Athletico PRvsPalmeirasBrasilien, Serie ABettingGuru1.84BettingGuru</t>
+          <t>13. okt.TidTipEkspertOdds18:45Sabah BakuvsSlavia PragChampions LeagueBettingGuru1.84BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15. okt.TidTipEkspertOdds18:45PanathinaikosvsBorac Banja LukaConference LeagueBettingGuru2.00BettingGuru</t>
+          <t>14. okt.TidTipEkspertOdds21:00Shakhtar DonetskvsAEK AthenChampions LeagueBettingGuru3.60BettingGuru</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15. okt.TidTipEkspertOdds18:45GentvsAGFUEFA, Conference LeagueBettingGuru1.72BettingGuru</t>
+          <t>15. okt.TidTipEkspertOdds18:45PanathinaikosvsBorac Banja LukaConference LeagueBettingGuru2.00BettingGuru</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14. okt.TidTipEkspertOdds21:00Shakhtar DonetskvsAEK AthenChampions LeagueBettingGuru3.60BettingGuru</t>
+          <t>18. okt.TidTipEkspertOdds00:30Athletico PRvsPalmeirasBrasilien, Serie ABettingGuru1.84BettingGuru</t>
         </is>
       </c>
     </row>
@@ -508,31 +508,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11. okt.TidTipEkspertOdds22:30GrêmiovsInternacionalBrasileirãoFrank Pilantra1.47Frank Pilantra</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
           <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>11. okt.TidTipEkspertOdds22:30FlamengovsFluminenseBrasileirãoFrank Pilantra2.10Frank Pilantra</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15. okt.TidTipEkspertOdds18:45GentvsAGFUEFA, Conference LeagueBettingGuru1.72BettingGuru</t>
+          <t>13. okt.TidTipEkspertOdds18:45Sabah BakuvsSlavia PragChampions LeagueBettingGuru1.84BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13. okt.TidTipEkspertOdds18:45Sabah BakuvsSlavia PragChampions LeagueBettingGuru1.84BettingGuru</t>
+          <t>14. okt.TidTipEkspertOdds21:00Shakhtar DonetskvsAEK AthenChampions LeagueBettingGuru3.60BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14. okt.TidTipEkspertOdds21:00Shakhtar DonetskvsAEK AthenChampions LeagueBettingGuru3.60BettingGuru</t>
+          <t>18. okt.TidTipEkspertOdds00:30Athletico PRvsPalmeirasBrasilien, Serie ABettingGuru1.84BettingGuru</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15. okt.TidTipEkspertOdds18:45PanathinaikosvsBorac Banja LukaConference LeagueBettingGuru2.00BettingGuru</t>
+          <t>15. okt.TidTipEkspertOdds18:45GentvsAGFUEFA, Conference LeagueBettingGuru1.72BettingGuru</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18. okt.TidTipEkspertOdds00:30Athletico PRvsPalmeirasBrasilien, Serie ABettingGuru1.84BettingGuru</t>
+          <t>15. okt.TidTipEkspertOdds18:45PanathinaikosvsBorac Banja LukaConference LeagueBettingGuru2.00BettingGuru</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,31 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>14. okt.TidTipEkspertOdds02:30Boca JuniorsvsVasco da GamaCopa SudamericanaFrank Pilantra1.98Frank Pilantra</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>18. okt.TidTipEkspertOdds02:00São PaulovsVasco da GamaBrasileirãoFrank Pilantra1.57Frank Pilantra</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14. okt.TidTipEkspertOdds21:00Shakhtar DonetskvsAEK AthenChampions LeagueBettingGuru3.60BettingGuru</t>
+          <t>15. okt.TidTipEkspertOdds18:45PanathinaikosvsBorac Banja LukaConference LeagueBettingGuru2.00BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18. okt.TidTipEkspertOdds00:30Athletico PRvsPalmeirasBrasilien, Serie ABettingGuru1.84BettingGuru</t>
+          <t>15. okt.TidTipEkspertOdds18:45GentvsAGFUEFA, Conference LeagueBettingGuru1.72BettingGuru</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15. okt.TidTipEkspertOdds18:45GentvsAGFUEFA, Conference LeagueBettingGuru1.72BettingGuru</t>
+          <t>18. okt.TidTipEkspertOdds00:30Athletico PRvsPalmeirasBrasilien, Serie ABettingGuru1.84BettingGuru</t>
         </is>
       </c>
     </row>
@@ -496,43 +496,79 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15. okt.TidTipEkspertOdds18:45PanathinaikosvsBorac Banja LukaConference LeagueBettingGuru2.00BettingGuru</t>
+          <t>14. okt.TidTipEkspertOdds21:00Shakhtar DonetskvsAEK AthenChampions LeagueBettingGuru3.60BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>frank-pilantra</t>
+          <t>loso</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14. okt.TidTipEkspertOdds02:30Boca JuniorsvsVasco da GamaCopa SudamericanaFrank Pilantra1.98Frank Pilantra</t>
+          <t>13. okt.TidTipEkspertOdds19:04Over 199,5 pointBC LuleåvsNässjöLoso6.50Loso</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>frank-pilantra</t>
+          <t>loso</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
+          <t>13. okt.TidTipEkspertOdds19:04Högsbo +8,5SödertäljevsHögsboLoso1.83Loso</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>loso</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>13. okt.TidTipEkspertOdds19:04Köping Stars -4,5Köping StarsvsUppsalaLoso1.78Loso</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>frank-pilantra</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>14. okt.TidTipEkspertOdds02:30Boca JuniorsvsVasco da GamaCopa SudamericanaFrank Pilantra1.98Frank Pilantra</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>18. okt.TidTipEkspertOdds02:00São PaulovsVasco da GamaBrasileirãoFrank Pilantra1.57Frank Pilantra</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13. okt.TidTipEkspertOdds18:45Sabah BakuvsSlavia PragChampions LeagueBettingGuru1.84BettingGuru</t>
+          <t>17. okt.TidTipEkspertOdds14:00SkivevsFA 2000CampoBet 3. DivisionBettingGuru1.98BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15. okt.TidTipEkspertOdds18:45PanathinaikosvsBorac Banja LukaConference LeagueBettingGuru2.00BettingGuru</t>
+          <t>18. okt.TidTipEkspertOdds00:30Athletico PRvsPalmeirasBrasilien, Serie ABettingGuru1.84BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15. okt.TidTipEkspertOdds18:45GentvsAGFUEFA, Conference LeagueBettingGuru1.72BettingGuru</t>
+          <t>14. okt.TidTipEkspertOdds21:00Shakhtar DonetskvsAEK AthenChampions LeagueBettingGuru3.60BettingGuru</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18. okt.TidTipEkspertOdds00:30Athletico PRvsPalmeirasBrasilien, Serie ABettingGuru1.84BettingGuru</t>
+          <t>15. okt.TidTipEkspertOdds18:45PanathinaikosvsBorac Banja LukaConference LeagueBettingGuru2.00BettingGuru</t>
         </is>
       </c>
     </row>
@@ -496,79 +496,43 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14. okt.TidTipEkspertOdds21:00Shakhtar DonetskvsAEK AthenChampions LeagueBettingGuru3.60BettingGuru</t>
+          <t>15. okt.TidTipEkspertOdds18:45GentvsAGFUEFA, Conference LeagueBettingGuru1.72BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>loso</t>
+          <t>frank-pilantra</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13. okt.TidTipEkspertOdds19:04Over 199,5 pointBC LuleåvsNässjöLoso6.50Loso</t>
+          <t>18. okt.TidTipEkspertOdds02:00São PaulovsVasco da GamaBrasileirãoFrank Pilantra1.57Frank Pilantra</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>loso</t>
+          <t>frank-pilantra</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13. okt.TidTipEkspertOdds19:04Högsbo +8,5SödertäljevsHögsboLoso1.83Loso</t>
+          <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>loso</t>
+          <t>frank-pilantra</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13. okt.TidTipEkspertOdds19:04Köping Stars -4,5Köping StarsvsUppsalaLoso1.78Loso</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
           <t>14. okt.TidTipEkspertOdds02:30Boca JuniorsvsVasco da GamaCopa SudamericanaFrank Pilantra1.98Frank Pilantra</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>18. okt.TidTipEkspertOdds02:00São PaulovsVasco da GamaBrasileirãoFrank Pilantra1.57Frank Pilantra</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17. okt.TidTipEkspertOdds14:00SkivevsFA 2000CampoBet 3. DivisionBettingGuru1.98BettingGuru</t>
+          <t>15. okt.TidTipEkspertOdds18:45GentvsAGFUEFA, Conference LeagueBettingGuru1.72BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18. okt.TidTipEkspertOdds00:30Athletico PRvsPalmeirasBrasilien, Serie ABettingGuru1.84BettingGuru</t>
+          <t>14. okt.TidTipEkspertOdds21:00Shakhtar DonetskvsAEK AthenChampions LeagueBettingGuru3.60BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14. okt.TidTipEkspertOdds21:00Shakhtar DonetskvsAEK AthenChampions LeagueBettingGuru3.60BettingGuru</t>
+          <t>16. okt.TidTipEkspertOdds19:00Aarhus FremadvsEsbjergBetinia LigaBettingGuru1.75BettingGuru</t>
         </is>
       </c>
     </row>
@@ -496,19 +496,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15. okt.TidTipEkspertOdds18:45GentvsAGFUEFA, Conference LeagueBettingGuru1.72BettingGuru</t>
+          <t>17. okt.TidTipEkspertOdds14:00SkivevsFA 2000CampoBet 3. DivisionBettingGuru1.98BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>frank-pilantra</t>
+          <t>bettingguru</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18. okt.TidTipEkspertOdds02:00São PaulovsVasco da GamaBrasileirãoFrank Pilantra1.57Frank Pilantra</t>
+          <t>18. okt.TidTipEkspertOdds00:30Athletico PRvsPalmeirasBrasilien, Serie ABettingGuru1.84BettingGuru</t>
         </is>
       </c>
     </row>
@@ -531,6 +531,30 @@
         </is>
       </c>
       <c r="B9" t="inlineStr">
+        <is>
+          <t>15. okt.TidTipEkspertOdds00:00Atletico MGvsMontevideo City TorqueCopa SudamericanaFrank Pilantra1.40Frank Pilantra</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>18. okt.TidTipEkspertOdds02:00São PaulovsVasco da GamaBrasileirãoFrank Pilantra1.57Frank Pilantra</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>14. okt.TidTipEkspertOdds02:30Boca JuniorsvsVasco da GamaCopa SudamericanaFrank Pilantra1.98Frank Pilantra</t>
         </is>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15. okt.TidTipEkspertOdds18:45GentvsAGFUEFA, Conference LeagueBettingGuru1.72BettingGuru</t>
+          <t>18. okt.TidTipEkspertOdds00:30Athletico PRvsPalmeirasBrasilien, Serie ABettingGuru1.84BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14. okt.TidTipEkspertOdds21:00Shakhtar DonetskvsAEK AthenChampions LeagueBettingGuru3.60BettingGuru</t>
+          <t>15. okt.TidTipEkspertOdds18:45PanathinaikosvsBorac Banja LukaConference LeagueBettingGuru2.00BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16. okt.TidTipEkspertOdds19:00Aarhus FremadvsEsbjergBetinia LigaBettingGuru1.75BettingGuru</t>
+          <t>17. okt.TidTipEkspertOdds16:00Manchester CityvsIpswichPremier LeagueBettingGuru2.10BettingGuru</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15. okt.TidTipEkspertOdds18:45PanathinaikosvsBorac Banja LukaConference LeagueBettingGuru2.00BettingGuru</t>
+          <t>16. okt.TidTipEkspertOdds19:00Aarhus FremadvsEsbjergBetinia LigaBettingGuru1.75BettingGuru</t>
         </is>
       </c>
     </row>
@@ -508,31 +508,31 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18. okt.TidTipEkspertOdds00:30Athletico PRvsPalmeirasBrasilien, Serie ABettingGuru1.84BettingGuru</t>
+          <t>14. okt.TidTipEkspertOdds21:00Shakhtar DonetskvsAEK AthenChampions LeagueBettingGuru3.60BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>frank-pilantra</t>
+          <t>bettingguru</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
+          <t>17. okt.TidTipEkspertOdds13:30AaBvsVejleBetinia LigaBettingGuru3.65BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>frank-pilantra</t>
+          <t>bettingguru</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>15. okt.TidTipEkspertOdds00:00Atletico MGvsMontevideo City TorqueCopa SudamericanaFrank Pilantra1.40Frank Pilantra</t>
+          <t>15. okt.TidTipEkspertOdds18:45GentvsAGFUEFA, Conference LeagueBettingGuru1.72BettingGuru</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18. okt.TidTipEkspertOdds02:00São PaulovsVasco da GamaBrasileirãoFrank Pilantra1.57Frank Pilantra</t>
+          <t>15. okt.TidTipEkspertOdds00:00Atletico MGvsMontevideo City TorqueCopa SudamericanaFrank Pilantra1.40Frank Pilantra</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14. okt.TidTipEkspertOdds02:30Boca JuniorsvsVasco da GamaCopa SudamericanaFrank Pilantra1.98Frank Pilantra</t>
+          <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>18. okt.TidTipEkspertOdds02:00São PaulovsVasco da GamaBrasileirãoFrank Pilantra1.57Frank Pilantra</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>18. okt.TidTipEkspertOdds00:30Athletico PRvsPalmeirasBrasilien, Serie ABettingGuru1.84BettingGuru</t>
+          <t>18. okt.TidTipEkspertOdds14:00Lyngby BKvsFC NordsjællandSuperligaBettingGuru2.30BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15. okt.TidTipEkspertOdds18:45PanathinaikosvsBorac Banja LukaConference LeagueBettingGuru2.00BettingGuru</t>
+          <t>17. okt.TidTipEkspertOdds14:00SkivevsFA 2000CampoBet 3. DivisionBettingGuru1.98BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>17. okt.TidTipEkspertOdds16:00Manchester CityvsIpswichPremier LeagueBettingGuru2.10BettingGuru</t>
+          <t>16. okt.TidTipEkspertOdds19:00Aarhus FremadvsEsbjergBetinia LigaBettingGuru1.75BettingGuru</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16. okt.TidTipEkspertOdds19:00Aarhus FremadvsEsbjergBetinia LigaBettingGuru1.75BettingGuru</t>
+          <t>17. okt.TidTipEkspertOdds16:00Manchester CityvsIpswichPremier LeagueBettingGuru2.10BettingGuru</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17. okt.TidTipEkspertOdds14:00SkivevsFA 2000CampoBet 3. DivisionBettingGuru1.98BettingGuru</t>
+          <t>18. okt.TidTipEkspertOdds00:30Athletico PRvsPalmeirasBrasilien, Serie ABettingGuru1.84BettingGuru</t>
         </is>
       </c>
     </row>
@@ -508,65 +508,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14. okt.TidTipEkspertOdds21:00Shakhtar DonetskvsAEK AthenChampions LeagueBettingGuru3.60BettingGuru</t>
+          <t>17. okt.TidTipEkspertOdds13:30AaBvsVejleBetinia LigaBettingGuru3.65BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>bettingguru</t>
+          <t>frank-pilantra</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
-        <is>
-          <t>17. okt.TidTipEkspertOdds13:30AaBvsVejleBetinia LigaBettingGuru3.65BettingGuru</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>bettingguru</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>15. okt.TidTipEkspertOdds18:45GentvsAGFUEFA, Conference LeagueBettingGuru1.72BettingGuru</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>15. okt.TidTipEkspertOdds00:00Atletico MGvsMontevideo City TorqueCopa SudamericanaFrank Pilantra1.40Frank Pilantra</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>14. okt.TidTipEkspertOdds22:00FluminensevsPalmeirasCopa LibertadoresFrank Pilantra1.50Frank Pilantra</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
         <is>
           <t>18. okt.TidTipEkspertOdds02:00São PaulovsVasco da GamaBrasileirãoFrank Pilantra1.57Frank Pilantra</t>
         </is>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>18. okt.TidTipEkspertOdds14:00Lyngby BKvsFC NordsjællandSuperligaBettingGuru2.30BettingGuru</t>
+          <t>17. okt.TidTipEkspertOdds14:00SkivevsFA 2000CampoBet 3. DivisionBettingGuru1.98BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>17. okt.TidTipEkspertOdds14:00SkivevsFA 2000CampoBet 3. DivisionBettingGuru1.98BettingGuru</t>
+          <t>16. okt.TidTipEkspertOdds19:00Aarhus FremadvsEsbjergBetinia LigaBettingGuru1.75BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16. okt.TidTipEkspertOdds19:00Aarhus FremadvsEsbjergBetinia LigaBettingGuru1.75BettingGuru</t>
+          <t>17. okt.TidTipEkspertOdds13:30AaBvsVejleBetinia LigaBettingGuru3.65BettingGuru</t>
         </is>
       </c>
     </row>
@@ -508,17 +508,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>17. okt.TidTipEkspertOdds13:30AaBvsVejleBetinia LigaBettingGuru3.65BettingGuru</t>
+          <t>18. okt.TidTipEkspertOdds14:00Lyngby BKvsFC NordsjællandSuperligaBettingGuru2.30BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>loso</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>16. okt.TidTipEkspertOdds19:30Over 3,25 målStocksundvsEnköpingLoso1.80Loso</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>frank-pilantra</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>18. okt.TidTipEkspertOdds02:00São PaulovsVasco da GamaBrasileirãoFrank Pilantra1.57Frank Pilantra</t>
         </is>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17. okt.TidTipEkspertOdds14:00SkivevsFA 2000CampoBet 3. DivisionBettingGuru1.98BettingGuru</t>
+          <t>16. okt.TidTipEkspertOdds19:00Aarhus FremadvsEsbjergBetinia LigaBettingGuru1.75BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16. okt.TidTipEkspertOdds19:00Aarhus FremadvsEsbjergBetinia LigaBettingGuru1.75BettingGuru</t>
+          <t>17. okt.TidTipEkspertOdds13:30AaBvsVejleBetinia LigaBettingGuru3.65BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>17. okt.TidTipEkspertOdds13:30AaBvsVejleBetinia LigaBettingGuru3.65BettingGuru</t>
+          <t>18. okt.TidTipEkspertOdds00:30Athletico PRvsPalmeirasBrasilien, Serie ABettingGuru1.84BettingGuru</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18. okt.TidTipEkspertOdds00:30Athletico PRvsPalmeirasBrasilien, Serie ABettingGuru1.84BettingGuru</t>
+          <t>17. okt.TidTipEkspertOdds14:00NæsbyvsVanløseCampoBet 3. DivisionBettingGuru1.78BettingGuru</t>
         </is>
       </c>
     </row>
@@ -515,22 +515,46 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>loso</t>
+          <t>bettingguru</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16. okt.TidTipEkspertOdds19:30Over 3,25 målStocksundvsEnköpingLoso1.80Loso</t>
+          <t>17. okt.TidTipEkspertOdds14:00SkivevsFA 2000CampoBet 3. DivisionBettingGuru1.98BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>loso</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>16. okt.TidTipEkspertOdds19:00Kalix -1,5KalixvsKirunaLoso1.95Loso</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>loso</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>16. okt.TidTipEkspertOdds19:30Over 3,25 målStocksundvsEnköpingLoso1.80Loso</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>frank-pilantra</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>18. okt.TidTipEkspertOdds02:00São PaulovsVasco da GamaBrasileirãoFrank Pilantra1.57Frank Pilantra</t>
         </is>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16. okt.TidTipEkspertOdds19:00Aarhus FremadvsEsbjergBetinia LigaBettingGuru1.75BettingGuru</t>
+          <t>18. okt.TidTipEkspertOdds00:30Athletico PRvsPalmeirasBrasilien, Serie ABettingGuru1.84BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>17. okt.TidTipEkspertOdds13:30AaBvsVejleBetinia LigaBettingGuru3.65BettingGuru</t>
+          <t>17. okt.TidTipEkspertOdds14:00NæsbyvsVanløseCampoBet 3. DivisionBettingGuru1.78BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18. okt.TidTipEkspertOdds00:30Athletico PRvsPalmeirasBrasilien, Serie ABettingGuru1.84BettingGuru</t>
+          <t>17. okt.TidTipEkspertOdds16:00Manchester CityvsIpswichPremier LeagueBettingGuru2.10BettingGuru</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17. okt.TidTipEkspertOdds16:00Manchester CityvsIpswichPremier LeagueBettingGuru2.10BettingGuru</t>
+          <t>17. okt.TidTipEkspertOdds14:00SkivevsFA 2000CampoBet 3. DivisionBettingGuru1.98BettingGuru</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17. okt.TidTipEkspertOdds14:00NæsbyvsVanløseCampoBet 3. DivisionBettingGuru1.78BettingGuru</t>
+          <t>18. okt.TidTipEkspertOdds14:00LyngbyvsFc NordsjællandSuperligaBettingGuru1.68BettingGuru</t>
         </is>
       </c>
     </row>
@@ -520,41 +520,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>17. okt.TidTipEkspertOdds14:00SkivevsFA 2000CampoBet 3. DivisionBettingGuru1.98BettingGuru</t>
+          <t>17. okt.TidTipEkspertOdds13:30AaBvsVejleBetinia LigaBettingGuru3.65BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>loso</t>
+          <t>frank-pilantra</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
-        <is>
-          <t>16. okt.TidTipEkspertOdds19:00Kalix -1,5KalixvsKirunaLoso1.95Loso</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>loso</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>16. okt.TidTipEkspertOdds19:30Over 3,25 målStocksundvsEnköpingLoso1.80Loso</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
         <is>
           <t>18. okt.TidTipEkspertOdds02:00São PaulovsVasco da GamaBrasileirãoFrank Pilantra1.57Frank Pilantra</t>
         </is>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>18. okt.TidTipEkspertOdds00:30Athletico PRvsPalmeirasBrasilien, Serie ABettingGuru1.84BettingGuru</t>
+          <t>17. okt.TidTipEkspertOdds14:00NæsbyvsVanløseCampoBet 3. DivisionBettingGuru1.78BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>17. okt.TidTipEkspertOdds14:00NæsbyvsVanløseCampoBet 3. DivisionBettingGuru1.78BettingGuru</t>
+          <t>17. okt.TidTipEkspertOdds16:00Manchester CityvsIpswichPremier LeagueBettingGuru2.10BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>17. okt.TidTipEkspertOdds16:00Manchester CityvsIpswichPremier LeagueBettingGuru2.10BettingGuru</t>
+          <t>17. okt.TidTipEkspertOdds13:30AaBvsVejleBetinia LigaBettingGuru3.65BettingGuru</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17. okt.TidTipEkspertOdds14:00SkivevsFA 2000CampoBet 3. DivisionBettingGuru1.98BettingGuru</t>
+          <t>18. okt.TidTipEkspertOdds00:30Athletico PRvsPalmeirasBrasilien, Serie ABettingGuru1.84BettingGuru</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18. okt.TidTipEkspertOdds14:00LyngbyvsFc NordsjællandSuperligaBettingGuru1.68BettingGuru</t>
+          <t>17. okt.TidTipEkspertOdds14:00SkivevsFA 2000CampoBet 3. DivisionBettingGuru1.98BettingGuru</t>
         </is>
       </c>
     </row>
@@ -520,17 +520,53 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>17. okt.TidTipEkspertOdds13:30AaBvsVejleBetinia LigaBettingGuru3.65BettingGuru</t>
+          <t>18. okt.TidTipEkspertOdds14:00LyngbyvsFc NordsjællandSuperligaBettingGuru1.68BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>loso</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>17. okt.TidTipEkspertOdds18:04Umeå under 69,5 pointBoråsvsUmeåLoso3.60Loso</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>loso</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>17. okt.TidTipEkspertOdds12:30Over 3,5 målLidingövsFrankeLoso2.02Loso</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>loso</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>17. okt.TidTipEkspertOdds16:00Hudiksvall -3,5HudiksvallvsArlanda WingsLoso1.72Loso</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>frank-pilantra</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>18. okt.TidTipEkspertOdds02:00São PaulovsVasco da GamaBrasileirãoFrank Pilantra1.57Frank Pilantra</t>
         </is>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17. okt.TidTipEkspertOdds14:00NæsbyvsVanløseCampoBet 3. DivisionBettingGuru1.78BettingGuru</t>
+          <t>18. okt.TidTipEkspertOdds14:00LyngbyvsFC NordsjællandSuperligaBettingGuru1.68BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>17. okt.TidTipEkspertOdds16:00Manchester CityvsIpswichPremier LeagueBettingGuru2.10BettingGuru</t>
+          <t>18. okt.TidTipEkspertOdds00:30Athletico PRvsPalmeirasBrasilien, Serie ABettingGuru1.84BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,101 +472,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>17. okt.TidTipEkspertOdds13:30AaBvsVejleBetinia LigaBettingGuru3.65BettingGuru</t>
+          <t>18. okt.TidTipEkspertOdds14:00Lyngby BKvsFC NordsjællandSuperligaBettingGuru2.30BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>bettingguru</t>
+          <t>loso</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18. okt.TidTipEkspertOdds00:30Athletico PRvsPalmeirasBrasilien, Serie ABettingGuru1.84BettingGuru</t>
+          <t>17. okt.TidTipEkspertOdds18:04Umeå under 69,5 pointBoråsvsUmeåLoso3.60Loso</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bettingguru</t>
+          <t>frank-pilantra</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
-        <is>
-          <t>17. okt.TidTipEkspertOdds14:00SkivevsFA 2000CampoBet 3. DivisionBettingGuru1.98BettingGuru</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>bettingguru</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>18. okt.TidTipEkspertOdds14:00Lyngby BKvsFC NordsjællandSuperligaBettingGuru2.30BettingGuru</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>bettingguru</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>18. okt.TidTipEkspertOdds14:00LyngbyvsFc NordsjællandSuperligaBettingGuru1.68BettingGuru</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>loso</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>17. okt.TidTipEkspertOdds18:04Umeå under 69,5 pointBoråsvsUmeåLoso3.60Loso</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>loso</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>17. okt.TidTipEkspertOdds12:30Over 3,5 målLidingövsFrankeLoso2.02Loso</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>loso</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>17. okt.TidTipEkspertOdds16:00Hudiksvall -3,5HudiksvallvsArlanda WingsLoso1.72Loso</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
         <is>
           <t>18. okt.TidTipEkspertOdds02:00São PaulovsVasco da GamaBrasileirãoFrank Pilantra1.57Frank Pilantra</t>
         </is>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>18. okt.TidTipEkspertOdds14:00LyngbyvsFC NordsjællandSuperligaBettingGuru1.68BettingGuru</t>
+          <t>20. okt.TidTipEkspertOdds21:00Manchester CityvsAEK AthenChampions LeagueBettingGuru1.83BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18. okt.TidTipEkspertOdds00:30Athletico PRvsPalmeirasBrasilien, Serie ABettingGuru1.84BettingGuru</t>
+          <t>18. okt.TidTipEkspertOdds14:00Lyngby BKvsFC NordsjællandSuperligaBettingGuru2.30BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,31 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18. okt.TidTipEkspertOdds14:00Lyngby BKvsFC NordsjællandSuperligaBettingGuru2.30BettingGuru</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>loso</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>17. okt.TidTipEkspertOdds18:04Umeå under 69,5 pointBoråsvsUmeåLoso3.60Loso</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>18. okt.TidTipEkspertOdds02:00São PaulovsVasco da GamaBrasileirãoFrank Pilantra1.57Frank Pilantra</t>
+          <t>18. okt.TidTipEkspertOdds14:00LyngbyvsFC NordsjællandSuperligaBettingGuru1.68BettingGuru</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20. okt.TidTipEkspertOdds21:00Manchester CityvsAEK AthenChampions LeagueBettingGuru1.83BettingGuru</t>
+          <t>18. okt.TidTipEkspertOdds14:00Lyngby BKvsFC NordsjællandSuperligaBettingGuru2.30BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18. okt.TidTipEkspertOdds14:00Lyngby BKvsFC NordsjællandSuperligaBettingGuru2.30BettingGuru</t>
+          <t>20. okt.TidTipEkspertOdds21:00Manchester CityvsAEK AthenChampions LeagueBettingGuru1.83BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,67 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>20. okt.TidTipEkspertOdds21:00RomavsSlovan BratislavaChampions LeagueBettingGuru1.96BettingGuru</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>bettingguru</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>18. okt.TidTipEkspertOdds14:00LyngbyvsFC NordsjællandSuperligaBettingGuru1.68BettingGuru</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>loso</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>18. okt.TidTipEkspertOdds14:00Over 3,5 målQvidingvsLindomeLoso1.75Loso</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>loso</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>18. okt.TidTipEkspertOdds14:00Over 5,5 målHanvikenvsTyringeLoso2.00Loso</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>loso</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>18. okt.TidTipEkspertOdds13:00Over 5,5 målVasalundvsAFC EskilstunaLoso6.00Loso</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>loso</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>18. okt.TidTipEkspertOdds14:00Over 3,25 målBöljanvsKongahällaLoso1.87Loso</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,96 +443,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>bettingguru</t>
+          <t>frank-pilantra</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>18. okt.TidTipEkspertOdds14:00Lyngby BKvsFC NordsjællandSuperligaBettingGuru2.30BettingGuru</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>bettingguru</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>20. okt.TidTipEkspertOdds21:00Manchester CityvsAEK AthenChampions LeagueBettingGuru1.83BettingGuru</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>bettingguru</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>20. okt.TidTipEkspertOdds21:00RomavsSlovan BratislavaChampions LeagueBettingGuru1.96BettingGuru</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>bettingguru</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>18. okt.TidTipEkspertOdds14:00LyngbyvsFC NordsjællandSuperligaBettingGuru1.68BettingGuru</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>loso</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>18. okt.TidTipEkspertOdds14:00Over 3,5 målQvidingvsLindomeLoso1.75Loso</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>loso</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>18. okt.TidTipEkspertOdds14:00Over 5,5 målHanvikenvsTyringeLoso2.00Loso</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>loso</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>18. okt.TidTipEkspertOdds13:00Over 5,5 målVasalundvsAFC EskilstunaLoso6.00Loso</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>loso</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>18. okt.TidTipEkspertOdds14:00Over 3,25 målBöljanvsKongahällaLoso1.87Loso</t>
+          <t>22. okt.TidTipEkspertOdds02:30PalmeirasvsFluminenseCopa LibertadoresFrank Pilantra1.67Frank Pilantra</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +447,18 @@
         </is>
       </c>
       <c r="B2" t="inlineStr">
+        <is>
+          <t>23. okt.TidTipEkspertOdds02:30FlamengovsEstudiantesCopa LibertadoresFrank Pilantra1.90Frank Pilantra</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>22. okt.TidTipEkspertOdds02:30PalmeirasvsFluminenseCopa LibertadoresFrank Pilantra1.67Frank Pilantra</t>
         </is>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23. okt.TidTipEkspertOdds02:30FlamengovsEstudiantesCopa LibertadoresFrank Pilantra1.90Frank Pilantra</t>
+          <t>30. okt.TidTipEkspertOdds00:00Vasco da GamavsFlamengoBrasileirãoFrank Pilantra1.50Frank Pilantra</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>22. okt.TidTipEkspertOdds02:30PalmeirasvsFluminenseCopa LibertadoresFrank Pilantra1.67Frank Pilantra</t>
+          <t>23. okt.TidTipEkspertOdds02:30FlamengovsEstudiantesCopa LibertadoresFrank Pilantra1.90Frank Pilantra</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,24 +443,48 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>frank-pilantra</t>
+          <t>loso</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30. okt.TidTipEkspertOdds00:00Vasco da GamavsFlamengoBrasileirãoFrank Pilantra1.50Frank Pilantra</t>
+          <t>24. okt.TidTipEkspertOdds16:00AIK -12AIKvsMalbasLoso1.83Loso</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>loso</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>24. okt.TidTipEkspertOdds17:00Over 19 hjørnespark (3-vejs)BragevsÖsterLoso23.00Loso</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>loso</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>24. okt.TidTipEkspertOdds15:00Mikkel Rygaard scorerHäckenvsDegerforsLoso4.50Loso</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>frank-pilantra</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>23. okt.TidTipEkspertOdds02:30FlamengovsEstudiantesCopa LibertadoresFrank Pilantra1.90Frank Pilantra</t>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>30. okt.TidTipEkspertOdds00:00Vasco da GamavsFlamengoBrasileirãoFrank Pilantra1.50Frank Pilantra</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>24. okt.TidTipEkspertOdds16:00AIK -12AIKvsMalbasLoso1.83Loso</t>
+          <t>25. okt.TidTipEkspertOdds15:00Sundsvall -2,5SundsvallvsEnköpingLoso1.85Loso</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>24. okt.TidTipEkspertOdds17:00Over 19 hjørnespark (3-vejs)BragevsÖsterLoso23.00Loso</t>
+          <t>25. okt.TidTipEkspertOdds16:00Over 5,5 målHanvikenvsGrumsLoso1.75Loso</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24. okt.TidTipEkspertOdds15:00Mikkel Rygaard scorerHäckenvsDegerforsLoso4.50Loso</t>
+          <t>25. okt.TidTipEkspertOdds16:00Over 12 hjørnespark (3-vejs)EnköpingvsPiteåLoso6.00Loso</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,48 +443,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>loso</t>
+          <t>frank-pilantra</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>25. okt.TidTipEkspertOdds15:00Sundsvall -2,5SundsvallvsEnköpingLoso1.85Loso</t>
+          <t>30. okt.TidTipEkspertOdds00:00Vasco da GamavsFlamengoBrasileirãoFrank Pilantra1.50Frank Pilantra</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>loso</t>
+          <t>frank-pilantra</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>25. okt.TidTipEkspertOdds16:00Over 5,5 målHanvikenvsGrumsLoso1.75Loso</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>loso</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>25. okt.TidTipEkspertOdds16:00Over 12 hjørnespark (3-vejs)EnköpingvsPiteåLoso6.00Loso</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>30. okt.TidTipEkspertOdds00:00Vasco da GamavsFlamengoBrasileirãoFrank Pilantra1.50Frank Pilantra</t>
+          <t>26. okt.TidTipEkspertOdds23:30CoritibavsGrêmioBrasileirãoFrank Pilantra1.70Frank Pilantra</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30. okt.TidTipEkspertOdds00:00Vasco da GamavsFlamengoBrasileirãoFrank Pilantra1.50Frank Pilantra</t>
+          <t>4. nov.TidTipEkspertOdds23:30Athletico PRvsVasco da GamaBrasileirãoFrank Pilantra1.47Frank Pilantra</t>
         </is>
       </c>
     </row>
@@ -461,6 +461,18 @@
       <c r="B3" t="inlineStr">
         <is>
           <t>26. okt.TidTipEkspertOdds23:30CoritibavsGrêmioBrasileirãoFrank Pilantra1.70Frank Pilantra</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>30. okt.TidTipEkspertOdds00:00Vasco da GamavsFlamengoBrasileirãoFrank Pilantra1.50Frank Pilantra</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,24 +443,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>frank-pilantra</t>
+          <t>bettingguru</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4. nov.TidTipEkspertOdds23:30Athletico PRvsVasco da GamaBrasileirãoFrank Pilantra1.47Frank Pilantra</t>
+          <t>28. okt.TidTipEkspertOdds17:00EsbjergvsFC NordsjællandDBU, PokalenBettingGuru2.30BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>frank-pilantra</t>
+          <t>bettingguru</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>26. okt.TidTipEkspertOdds23:30CoritibavsGrêmioBrasileirãoFrank Pilantra1.70Frank Pilantra</t>
+          <t>28. okt.TidTipEkspertOdds20:00RoskildevsAGFPokalturneringenBettingGuru2.00BettingGuru</t>
         </is>
       </c>
     </row>
@@ -471,6 +471,30 @@
         </is>
       </c>
       <c r="B4" t="inlineStr">
+        <is>
+          <t>26. okt.TidTipEkspertOdds23:30CoritibavsGrêmioBrasileirãoFrank Pilantra1.70Frank Pilantra</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>4. nov.TidTipEkspertOdds23:30Athletico PRvsVasco da GamaBrasileirãoFrank Pilantra1.47Frank Pilantra</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>30. okt.TidTipEkspertOdds00:00Vasco da GamavsFlamengoBrasileirãoFrank Pilantra1.50Frank Pilantra</t>
         </is>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>28. okt.TidTipEkspertOdds17:00EsbjergvsFC NordsjællandDBU, PokalenBettingGuru2.30BettingGuru</t>
+          <t>28. okt.TidTipEkspertOdds20:00RoskildevsAGFPokalturneringenBettingGuru2.00BettingGuru</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>28. okt.TidTipEkspertOdds20:00RoskildevsAGFPokalturneringenBettingGuru2.00BettingGuru</t>
+          <t>28. okt.TidTipEkspertOdds17:00EsbjergvsFC NordsjællandBetano PokalturneringenBettingGuru2.30BettingGuru</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>26. okt.TidTipEkspertOdds23:30CoritibavsGrêmioBrasileirãoFrank Pilantra1.70Frank Pilantra</t>
+          <t>30. okt.TidTipEkspertOdds00:00Vasco da GamavsFlamengoBrasileirãoFrank Pilantra1.50Frank Pilantra</t>
         </is>
       </c>
     </row>
@@ -485,18 +485,6 @@
       <c r="B5" t="inlineStr">
         <is>
           <t>4. nov.TidTipEkspertOdds23:30Athletico PRvsVasco da GamaBrasileirãoFrank Pilantra1.47Frank Pilantra</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>frank-pilantra</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>30. okt.TidTipEkspertOdds00:00Vasco da GamavsFlamengoBrasileirãoFrank Pilantra1.50Frank Pilantra</t>
         </is>
       </c>
     </row>

--- a/betting_tips.xlsx
+++ b/betting_tips.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,22 +467,46 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>frank-pilantra</t>
+          <t>bettingguru</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30. okt.TidTipEkspertOdds00:00Vasco da GamavsFlamengoBrasileirãoFrank Pilantra1.50Frank Pilantra</t>
+          <t>1. nov.TidTipEkspertOdds15:00Aarhus FremadvsHillerødBetinia LigaBettingGuru1.82BettingGuru</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>bettingguru</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1. nov.TidTipEkspertOdds13:00ThistedvsB93CampoBet 2. DivisionBettingGuru1.95BettingGuru</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>frank-pilantra</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>30. okt.TidTipEkspertOdds00:00Vasco da GamavsFlamengoBrasileirãoFrank Pilantra1.50Frank Pilantra</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>frank-pilantra</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>4. nov.TidTipEkspertOdds23:30Athletico PRvsVasco da GamaBrasileirãoFrank Pilantra1.47Frank Pilantra</t>
         </is>
